--- a/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
@@ -7,27 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAKIT_GIRISLERI" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAKIT_CIKISLARI" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAFTALIK_PLAN" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="17" state="hidden" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="18" state="hidden" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="19" state="hidden" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="20" state="hidden" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="21" state="hidden" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAKIT_GIRISLERI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAKIT_CIKISLARI" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HAFTALIK_PLAN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KARAR_MOTORU" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO_DUYARLILIK" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAPOR" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TESTLER" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGISIKLIK_KAYDI" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="AsgariTampon" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$15</definedName>
@@ -98,8 +97,7 @@
     <definedName name="VeriKaliteSkor" hidden="0" function="0" vbProcedure="0">KONTROLLER!$B$6</definedName>
     <definedName name="VeriKaliteYuksek" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$17</definedName>
     <definedName name="YogunlasmaEsigi" hidden="0" function="0" vbProcedure="0">AYARLAR!$B$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'PANO'!$A$1:$Z$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'RAPOR'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'RAPOR'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -107,14 +105,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="82">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -446,8 +445,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -502,8 +683,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -525,6 +772,346 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -536,7 +1123,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="215">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -937,6 +1524,163 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="63" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="71" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="70" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="70" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="71" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="70" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="70" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="72" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1224,7 +1968,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1371,7 +2115,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1518,7 +2262,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1608,7 +2352,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1641,494 +2385,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Dönem Başı ve Sonu Bakiye</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!G5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Dönem Başı Bakiye</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$G$6:$G$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>500000</v>
-                </pt>
-                <pt idx="1">
-                  <v>530000</v>
-                </pt>
-                <pt idx="2">
-                  <v>645000</v>
-                </pt>
-                <pt idx="3">
-                  <v>720000</v>
-                </pt>
-                <pt idx="4">
-                  <v>810000</v>
-                </pt>
-                <pt idx="5">
-                  <v>890000</v>
-                </pt>
-                <pt idx="6">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="7">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="8">
-                  <v>1135000</v>
-                </pt>
-                <pt idx="9">
-                  <v>1150000</v>
-                </pt>
-                <pt idx="10">
-                  <v>1215000</v>
-                </pt>
-                <pt idx="11">
-                  <v>1315000</v>
-                </pt>
-                <pt idx="12">
-                  <v>1385000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!H5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Dönem Sonu Bakiye</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C0504D"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$H$6:$H$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>530000</v>
-                </pt>
-                <pt idx="1">
-                  <v>645000</v>
-                </pt>
-                <pt idx="2">
-                  <v>720000</v>
-                </pt>
-                <pt idx="3">
-                  <v>810000</v>
-                </pt>
-                <pt idx="4">
-                  <v>890000</v>
-                </pt>
-                <pt idx="5">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="6">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="7">
-                  <v>1135000</v>
-                </pt>
-                <pt idx="8">
-                  <v>1150000</v>
-                </pt>
-                <pt idx="9">
-                  <v>1215000</v>
-                </pt>
-                <pt idx="10">
-                  <v>1315000</v>
-                </pt>
-                <pt idx="11">
-                  <v>1385000</v>
-                </pt>
-                <pt idx="12">
-                  <v>1415000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="64033880"/>
-        <axId val="41651033"/>
-      </barChart>
-      <catAx>
-        <axId val="64033880"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="41651033"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41651033"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="64033880"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2241,7 +2498,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2396,7 +2653,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2452,7 +2709,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2485,7 +2742,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2589,7 +2846,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2736,7 +2993,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2792,7 +3049,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -2825,7 +3082,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2954,7 +3211,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -2981,7 +3238,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3008,7 +3265,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3033,7 +3290,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3108,2719 +3365,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Haftalık Giriş / Çıkış</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!D5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Toplam Giriş</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$D$6:$D$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>205000</v>
-                </pt>
-                <pt idx="1">
-                  <v>205000</v>
-                </pt>
-                <pt idx="2">
-                  <v>330000</v>
-                </pt>
-                <pt idx="3">
-                  <v>220000</v>
-                </pt>
-                <pt idx="4">
-                  <v>165000</v>
-                </pt>
-                <pt idx="5">
-                  <v>200000</v>
-                </pt>
-                <pt idx="6">
-                  <v>175000</v>
-                </pt>
-                <pt idx="7">
-                  <v>200000</v>
-                </pt>
-                <pt idx="8">
-                  <v>155000</v>
-                </pt>
-                <pt idx="9">
-                  <v>195000</v>
-                </pt>
-                <pt idx="10">
-                  <v>180000</v>
-                </pt>
-                <pt idx="11">
-                  <v>205000</v>
-                </pt>
-                <pt idx="12">
-                  <v>205000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!E5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Toplam Çıkış</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="C0504D"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$E$6:$E$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>175000</v>
-                </pt>
-                <pt idx="1">
-                  <v>90000</v>
-                </pt>
-                <pt idx="2">
-                  <v>255000</v>
-                </pt>
-                <pt idx="3">
-                  <v>130000</v>
-                </pt>
-                <pt idx="4">
-                  <v>85000</v>
-                </pt>
-                <pt idx="5">
-                  <v>60000</v>
-                </pt>
-                <pt idx="6">
-                  <v>175000</v>
-                </pt>
-                <pt idx="7">
-                  <v>95000</v>
-                </pt>
-                <pt idx="8">
-                  <v>140000</v>
-                </pt>
-                <pt idx="9">
-                  <v>130000</v>
-                </pt>
-                <pt idx="10">
-                  <v>80000</v>
-                </pt>
-                <pt idx="11">
-                  <v>135000</v>
-                </pt>
-                <pt idx="12">
-                  <v>175000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="15461773"/>
-        <axId val="96889201"/>
-      </barChart>
-      <catAx>
-        <axId val="15461773"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="96889201"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="96889201"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1300" b="0" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr sz="1000" b="1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>₺</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="15461773"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Dönem Sonu Bakiye Eğilimi</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!H5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Dönem Sonu Bakiye</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4A7EBB"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:solidFill>
-                <a:srgbClr val="4A7EBB"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="r"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$H$6:$H$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>530000</v>
-                </pt>
-                <pt idx="1">
-                  <v>645000</v>
-                </pt>
-                <pt idx="2">
-                  <v>720000</v>
-                </pt>
-                <pt idx="3">
-                  <v>810000</v>
-                </pt>
-                <pt idx="4">
-                  <v>890000</v>
-                </pt>
-                <pt idx="5">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="6">
-                  <v>1030000</v>
-                </pt>
-                <pt idx="7">
-                  <v>1135000</v>
-                </pt>
-                <pt idx="8">
-                  <v>1150000</v>
-                </pt>
-                <pt idx="9">
-                  <v>1215000</v>
-                </pt>
-                <pt idx="10">
-                  <v>1315000</v>
-                </pt>
-                <pt idx="11">
-                  <v>1385000</v>
-                </pt>
-                <pt idx="12">
-                  <v>1415000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="1"/>
-        </ser>
-        <hiLowLines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </hiLowLines>
-        <marker val="0"/>
-        <axId val="60702563"/>
-        <axId val="30171811"/>
-      </lineChart>
-      <catAx>
-        <axId val="60702563"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="30171811"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="30171811"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="60702563"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Haftalık Net Nakit Akışı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>HAFTALIK_PLAN!F5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Net Akış</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>HAFTALIK_PLAN!$A$6:$A$18</f>
-              <strCache>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>HAFTALIK_PLAN!$F$6:$F$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>30000</v>
-                </pt>
-                <pt idx="1">
-                  <v>115000</v>
-                </pt>
-                <pt idx="2">
-                  <v>75000</v>
-                </pt>
-                <pt idx="3">
-                  <v>90000</v>
-                </pt>
-                <pt idx="4">
-                  <v>80000</v>
-                </pt>
-                <pt idx="5">
-                  <v>140000</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>105000</v>
-                </pt>
-                <pt idx="8">
-                  <v>15000</v>
-                </pt>
-                <pt idx="9">
-                  <v>65000</v>
-                </pt>
-                <pt idx="10">
-                  <v>100000</v>
-                </pt>
-                <pt idx="11">
-                  <v>70000</v>
-                </pt>
-                <pt idx="12">
-                  <v>30000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <overlap val="0"/>
-        <axId val="90840365"/>
-        <axId val="23610641"/>
-      </barChart>
-      <catAx>
-        <axId val="90840365"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="23610641"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="23610641"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-          </a:p>
-        </txPr>
-        <crossAx val="90840365"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Giriş Kaynağı Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>NAKIT_GIRISLERI!E5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Tutar (₺)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="416A9C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9F423F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="809B49"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6A5286"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="4"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3E8EA4"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="CC7C3A"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="6"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="8"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="9"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="8064A2"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="10"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4BACC6"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="11"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="F79646"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="12"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="AABAD7"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="3"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="4"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="5"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="6"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="7"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="8"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="9"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="10"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="11"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="12"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>NAKIT_GIRISLERI!$D$5:$D$18</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>Kaynak</v>
-                </pt>
-                <pt idx="1">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="2">
-                  <v>SATIŞ</v>
-                </pt>
-                <pt idx="3">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="4">
-                  <v>SATIŞ</v>
-                </pt>
-                <pt idx="5">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="6">
-                  <v>SATIŞ</v>
-                </pt>
-                <pt idx="7">
-                  <v>FİNANSMAN</v>
-                </pt>
-                <pt idx="8">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="9">
-                  <v>SATIŞ</v>
-                </pt>
-                <pt idx="10">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="11">
-                  <v>SATIŞ</v>
-                </pt>
-                <pt idx="12">
-                  <v>MÜŞTERİ TAHSİLATI</v>
-                </pt>
-                <pt idx="13">
-                  <v>SATIŞ</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>NAKIT_GIRISLERI!$E$6:$E$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>85000</v>
-                </pt>
-                <pt idx="1">
-                  <v>120000</v>
-                </pt>
-                <pt idx="2">
-                  <v>95000</v>
-                </pt>
-                <pt idx="3">
-                  <v>110000</v>
-                </pt>
-                <pt idx="4">
-                  <v>80000</v>
-                </pt>
-                <pt idx="5">
-                  <v>100000</v>
-                </pt>
-                <pt idx="6">
-                  <v>150000</v>
-                </pt>
-                <pt idx="7">
-                  <v>90000</v>
-                </pt>
-                <pt idx="8">
-                  <v>130000</v>
-                </pt>
-                <pt idx="9">
-                  <v>70000</v>
-                </pt>
-                <pt idx="10">
-                  <v>95000</v>
-                </pt>
-                <pt idx="11">
-                  <v>110000</v>
-                </pt>
-                <pt idx="12">
-                  <v>90000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1300" b="0" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr sz="1800" b="1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:uFillTx/>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Çıkış Kalemi Dağılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>NAKIT_CIKISLARI!E5</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Tutar (₺)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <explosion val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="416A9C"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9F423F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="809B49"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="6A5286"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="4"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3E8EA4"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="CC7C3A"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="6"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4F81BD"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C0504D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="8"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9BBB59"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="9"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="8064A2"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="10"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4BACC6"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="11"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="F79646"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="12"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="AABAD7"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12600">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="1"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="3"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="4"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="5"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="6"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="7"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="8"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="9"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="10"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="11"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="12"/>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="1000" b="0" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:uFillTx/>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                </a:p>
-              </txPr>
-              <dLblPos val="bestFit"/>
-              <showLegendKey val="0"/>
-              <showVal val="0"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-            </dLbl>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </txPr>
-            <dLblPos val="bestFit"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showLeaderLines val="1"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>NAKIT_CIKISLARI!$C$5:$C$18</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>Kalem</v>
-                </pt>
-                <pt idx="1">
-                  <v>MAAŞ</v>
-                </pt>
-                <pt idx="2">
-                  <v>KİRA</v>
-                </pt>
-                <pt idx="3">
-                  <v>TEDARİKÇİ</v>
-                </pt>
-                <pt idx="4">
-                  <v>VERGİ</v>
-                </pt>
-                <pt idx="5">
-                  <v>SGK</v>
-                </pt>
-                <pt idx="6">
-                  <v>MAAŞ</v>
-                </pt>
-                <pt idx="7">
-                  <v>TEDARİKÇİ</v>
-                </pt>
-                <pt idx="8">
-                  <v>KREDİ TAKSİTİ</v>
-                </pt>
-                <pt idx="9">
-                  <v>MAAŞ</v>
-                </pt>
-                <pt idx="10">
-                  <v>KİRA</v>
-                </pt>
-                <pt idx="11">
-                  <v>TEDARİKÇİ</v>
-                </pt>
-                <pt idx="12">
-                  <v>VERGİ</v>
-                </pt>
-                <pt idx="13">
-                  <v>MAAŞ</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>NAKIT_CIKISLARI!$E$6:$E$18</f>
-              <numCache>
-                <formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</formatCode>
-                <ptCount val="13"/>
-                <pt idx="0">
-                  <v>130000</v>
-                </pt>
-                <pt idx="1">
-                  <v>45000</v>
-                </pt>
-                <pt idx="2">
-                  <v>90000</v>
-                </pt>
-                <pt idx="3">
-                  <v>180000</v>
-                </pt>
-                <pt idx="4">
-                  <v>75000</v>
-                </pt>
-                <pt idx="5">
-                  <v>130000</v>
-                </pt>
-                <pt idx="6">
-                  <v>85000</v>
-                </pt>
-                <pt idx="7">
-                  <v>60000</v>
-                </pt>
-                <pt idx="8">
-                  <v>130000</v>
-                </pt>
-                <pt idx="9">
-                  <v>45000</v>
-                </pt>
-                <pt idx="10">
-                  <v>95000</v>
-                </pt>
-                <pt idx="11">
-                  <v>140000</v>
-                </pt>
-                <pt idx="12">
-                  <v>130000</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -8398,173 +5943,6 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>21</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>36</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>34</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>51</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>66</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>64</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>81</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="5" name="Chart 5"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>79</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>20</col>
-      <colOff>255600</colOff>
-      <row>96</row>
-      <rowOff>720</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="6" name="Chart 6"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -8811,351 +6189,575 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="57" min="1" max="1"/>
-    <col width="16" customWidth="1" style="57" min="2" max="2"/>
-    <col width="20" customWidth="1" style="57" min="3" max="3"/>
-    <col width="20" customWidth="1" style="57" min="4" max="4"/>
-    <col width="20" customWidth="1" style="57" min="5" max="5"/>
-    <col width="14" customWidth="1" style="57" min="6" max="6"/>
-    <col width="22" customWidth="1" style="57" min="7" max="7"/>
-    <col width="14" customWidth="1" style="57" min="8" max="8"/>
-    <col width="16" customWidth="1" style="57" min="9" max="9"/>
+    <col width="3" customWidth="1" style="57" min="1" max="1"/>
+    <col width="18" customWidth="1" style="57" min="2" max="2"/>
+    <col width="15" customWidth="1" style="57" min="3" max="3"/>
+    <col width="12" customWidth="1" style="57" min="4" max="4"/>
+    <col width="16" customWidth="1" style="57" min="5" max="5"/>
+    <col width="18" customWidth="1" style="57" min="6" max="6"/>
+    <col width="6" customWidth="1" style="57" min="7" max="7"/>
+    <col width="24" customWidth="1" style="57" min="8" max="8"/>
+    <col width="15" customWidth="1" style="57" min="9" max="9"/>
+    <col width="14" customWidth="1" style="57" min="10" max="10"/>
+    <col width="12" customWidth="1" style="57" min="11" max="11"/>
+    <col width="18" customWidth="1" style="57" min="12" max="12"/>
+    <col width="18" customWidth="1" style="57" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="58" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — NAKİT AKIŞI VE LİKİDİTE KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="59" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="138" t="inlineStr">
+        <is>
+          <t>13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="139" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="140" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="141" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="142" t="inlineStr">
+        <is>
+          <t>TOPLAM NAKİT HAVUZU</t>
+        </is>
+      </c>
+      <c r="C5" s="143" t="n"/>
+      <c r="D5" s="144" t="inlineStr">
+        <is>
+          <t>4 HESAP</t>
+        </is>
+      </c>
+      <c r="E5" s="145" t="inlineStr">
+        <is>
+          <t>BU AY ÖDENECEK ÇIKIŞ</t>
+        </is>
+      </c>
+      <c r="F5" s="143" t="n"/>
+      <c r="G5" s="146" t="inlineStr">
+        <is>
+          <t>VADE: 4 GÜN</t>
+        </is>
+      </c>
+      <c r="H5" s="142" t="inlineStr">
+        <is>
+          <t>NET SERBEST LİKİDİTE</t>
+        </is>
+      </c>
+      <c r="I5" s="143" t="n"/>
+      <c r="J5" s="147" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="148" t="inlineStr">
+        <is>
+          <t>DSCR / NAKİT DÖNGÜSÜ</t>
+        </is>
+      </c>
+      <c r="L5" s="143" t="n"/>
+      <c r="M5" s="144" t="inlineStr">
+        <is>
+          <t>EŞİK: 1.30x</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="60" t="inlineStr">
-        <is>
-          <t>LİKİDİTE &amp; SERBEST NAKİT</t>
-        </is>
-      </c>
-      <c r="D6" s="60" t="inlineStr">
-        <is>
-          <t>OPERASYONEL NET MARJ</t>
-        </is>
-      </c>
-      <c r="F6" s="60" t="inlineStr">
-        <is>
-          <t>ERKEN UYARI RİSK RADARI</t>
-        </is>
-      </c>
-      <c r="H6" s="61" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="149" t="n"/>
+      <c r="C6" s="143" t="n"/>
+      <c r="D6" s="143" t="n"/>
+      <c r="E6" s="150" t="n"/>
+      <c r="F6" s="143" t="n"/>
+      <c r="G6" s="143" t="n"/>
+      <c r="H6" s="149" t="n"/>
+      <c r="I6" s="143" t="n"/>
+      <c r="J6" s="143" t="n"/>
+      <c r="K6" s="151" t="n"/>
+      <c r="L6" s="143" t="n"/>
+      <c r="M6" s="143" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="62" t="inlineStr">
-        <is>
-          <t>₺ 14.850.000</t>
-        </is>
-      </c>
-      <c r="D7" s="62" t="inlineStr">
-        <is>
-          <t>% 28,4</t>
-        </is>
-      </c>
-      <c r="F7" s="63" t="inlineStr">
-        <is>
-          <t>DÜŞÜK RİSK (A+)</t>
-        </is>
-      </c>
-      <c r="H7" s="64" t="inlineStr">
-        <is>
-          <t>Q4 vadeli alacak tahsilatını hızlandır; nakit rezervini faiz artışına karşı koru.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="152" t="inlineStr">
+        <is>
+          <t>₺34.850.000</t>
+        </is>
+      </c>
+      <c r="C7" s="143" t="n"/>
+      <c r="D7" s="143" t="n"/>
+      <c r="E7" s="153" t="inlineStr">
+        <is>
+          <t>₺2.480.000</t>
+        </is>
+      </c>
+      <c r="F7" s="143" t="n"/>
+      <c r="G7" s="143" t="n"/>
+      <c r="H7" s="152" t="inlineStr">
+        <is>
+          <t>₺18.420.000</t>
+        </is>
+      </c>
+      <c r="I7" s="143" t="n"/>
+      <c r="J7" s="143" t="n"/>
+      <c r="K7" s="154" t="inlineStr">
+        <is>
+          <t>2.14x</t>
+        </is>
+      </c>
+      <c r="L7" s="143" t="n"/>
+      <c r="M7" s="143" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="149" t="n"/>
+      <c r="C8" s="143" t="n"/>
+      <c r="D8" s="143" t="n"/>
+      <c r="E8" s="150" t="n"/>
+      <c r="F8" s="143" t="n"/>
+      <c r="G8" s="143" t="n"/>
+      <c r="H8" s="149" t="n"/>
+      <c r="I8" s="143" t="n"/>
+      <c r="J8" s="143" t="n"/>
+      <c r="K8" s="151" t="n"/>
+      <c r="L8" s="143" t="n"/>
+      <c r="M8" s="143" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="65" t="inlineStr">
-        <is>
-          <t>Hedef: ₺ 12.000.000 | DURUM: GÜVENLİ (+23%)</t>
-        </is>
-      </c>
-      <c r="D9" s="66" t="inlineStr">
-        <is>
-          <t>Sektör Ortalaması: % 21,5 | DURUM: LİDER</t>
-        </is>
-      </c>
-      <c r="F9" s="67" t="inlineStr">
-        <is>
-          <t>Stres Testi Dayanımı: 180 Gün</t>
+      <c r="B9" s="155" t="inlineStr">
+        <is>
+          <t>↑ %14.2 konsolide vadesiz + fon</t>
+        </is>
+      </c>
+      <c r="C9" s="143" t="n"/>
+      <c r="D9" s="143" t="n"/>
+      <c r="E9" s="156" t="inlineStr">
+        <is>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="n"/>
+      <c r="G9" s="143" t="n"/>
+      <c r="H9" s="155" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %52.8 ORAN</t>
+        </is>
+      </c>
+      <c r="I9" s="143" t="n"/>
+      <c r="J9" s="143" t="n"/>
+      <c r="K9" s="157" t="inlineStr">
+        <is>
+          <t>✓ İDEAL borç servis karşılama</t>
+        </is>
+      </c>
+      <c r="L9" s="143" t="n"/>
+      <c r="M9" s="143" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="158" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="81" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="68" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="69" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="80" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="159" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="69" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="69" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="69" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="69" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="69" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="69" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="69" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="70" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="71" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="71" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="72">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="73">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="71" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="74" t="n">
+      <c r="C14" s="159" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="159" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="159" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="160" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="160" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="160" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="160" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="160" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="80" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="80" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="80" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="161" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="161" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="162" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="163" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="147" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="80" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="80" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="80" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="161" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="161" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="162" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="163" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="144" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="80" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="80" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="80" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="161" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="161" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="162" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="163" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="164" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="80" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="80" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="80" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="80" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="161" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="161" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="162" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="163" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="147" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="80" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="80" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="80" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="165" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="166" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="167" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="168" t="inlineStr"/>
+      <c r="L19" s="169" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="80" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="70" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="71" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="71" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="72">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="73">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="71" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="74" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="70" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="71" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="71" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="72">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="73">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="71" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="74" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="70" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="71" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="71" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="72">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="73">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="71" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="74" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="71" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="71" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="72">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="73">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="71" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="74" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="70" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="71" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="71" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="72">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="73">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="71" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="74" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="75" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="80" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="80" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="170" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="170" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="171" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="172" t="n"/>
+      <c r="M22" s="172" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="80" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="173" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="174" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="172" t="n"/>
+      <c r="M23" s="172" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="66" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="80" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="173" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="175" t="inlineStr">
+        <is>
+          <t>Atıl kalan ₺4.2M nakit rezervinin gecelik repoda değerlendirilmesiyle ek getiri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="176" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="65" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="177" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="178" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="179" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9618,247 +7220,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN42"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="30" customWidth="1" style="83" min="1" max="1"/>
-    <col width="26" customWidth="1" style="83" min="2" max="2"/>
-    <col width="20" customWidth="1" style="83" min="4" max="4"/>
-    <col width="16" customWidth="1" style="83" min="5" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
-        <is>
-          <t>PANO — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="57">
-      <c r="A3" s="122" t="inlineStr">
-        <is>
-          <t>YÖNETİCİ ÖZETİ — tek ekranda karar</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="57">
-      <c r="A5" s="116" t="inlineStr">
-        <is>
-          <t>Dönem Sonu Bakiye</t>
-        </is>
-      </c>
-      <c r="B5" s="120">
-        <f>KARAR_MOTORU!$B$5</f>
-        <v/>
-      </c>
-      <c r="D5" s="123" t="inlineStr">
-        <is>
-          <t>ÖNEMLİ UYARILAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="57">
-      <c r="A6" s="116" t="inlineStr">
-        <is>
-          <t>Net Nakit Akışı</t>
-        </is>
-      </c>
-      <c r="B6" s="120">
-        <f>KARAR_MOTORU!$B$14</f>
-        <v/>
-      </c>
-      <c r="D6" s="119" t="inlineStr">
-        <is>
-          <t>Bu sistem tahmin ve planlama aracıdır; kesin finansal tavsiye değildir. Gerçekleşme tahminlerden sapabilir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="57">
-      <c r="A7" s="116" t="inlineStr">
-        <is>
-          <t>Para Bitiş Haftası</t>
-        </is>
-      </c>
-      <c r="B7" s="118">
-        <f>IF(KARAR_MOTORU!$B$6&gt;0,KARAR_MOTORU!$B$6&amp;". hafta","Yok")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="57">
-      <c r="A8" s="116" t="inlineStr">
-        <is>
-          <t>İlk Risk Haftası</t>
-        </is>
-      </c>
-      <c r="B8" s="118">
-        <f>IF(KARAR_MOTORU!$B$7&gt;0,KARAR_MOTORU!$B$7&amp;". hafta","Yok")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="57">
-      <c r="A9" s="116" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B9" s="118">
-        <f>KARAR_MOTORU!$B$8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="57">
-      <c r="A10" s="116" t="inlineStr">
-        <is>
-          <t>Risk Seviyesi</t>
-        </is>
-      </c>
-      <c r="B10" s="118">
-        <f>KARAR_MOTORU!$B$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="57">
-      <c r="A11" s="116" t="inlineStr">
-        <is>
-          <t>Karar Gerekçesi</t>
-        </is>
-      </c>
-      <c r="B11" s="118">
-        <f>KARAR_MOTORU!$B$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="57">
-      <c r="A12" s="116" t="inlineStr">
-        <is>
-          <t>Toplam Beklenen Giriş</t>
-        </is>
-      </c>
-      <c r="B12" s="120">
-        <f>KARAR_MOTORU!$B$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="57">
-      <c r="A13" s="116" t="inlineStr">
-        <is>
-          <t>Toplam Planlanan Çıkış</t>
-        </is>
-      </c>
-      <c r="B13" s="120">
-        <f>KARAR_MOTORU!$B$13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="57">
-      <c r="A14" s="116" t="inlineStr">
-        <is>
-          <t>Kayıt Sayısı (Giriş+Çıkış)</t>
-        </is>
-      </c>
-      <c r="B14" s="117">
-        <f>KARAR_MOTORU!$B$18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="57">
-      <c r="A15" s="116" t="inlineStr">
-        <is>
-          <t>Veri Kalite Skoru</t>
-        </is>
-      </c>
-      <c r="B15" s="117">
-        <f>KONTROLLER!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="57">
-      <c r="A16" s="116" t="inlineStr">
-        <is>
-          <t>Önerilen Önlem</t>
-        </is>
-      </c>
-      <c r="B16" s="118">
-        <f>KARAR_MOTORU!$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="57">
-      <c r="A42" s="83" t="inlineStr">
-        <is>
-          <t>KuyrukKanit</t>
-        </is>
-      </c>
-      <c r="B42" s="83">
-        <f>IFERROR(COUNTIF($A$1:$A$1000,"&lt;&gt;"),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="2">
-    <mergeCell ref="D6:K7"/>
-    <mergeCell ref="A1:AN1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="cellIs" rank="0" priority="3" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6">
-    <cfRule type="cellIs" rank="0" priority="4" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="6" equalAverage="0" operator="equal" aboveAverage="0" dxfId="11" text="" percent="0" bottom="0">
-      <formula>"İNCELE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="7" equalAverage="0" operator="equal" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
-      <formula>"DURDUR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
-    <cfRule type="cellIs" rank="0" priority="8" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
-      <formula>50</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="9" equalAverage="0" operator="between" aboveAverage="0" dxfId="11" text="" percent="0" bottom="0">
-      <formula>50</formula>
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" rank="0" priority="10" equalAverage="0" operator="greaterThanOrEqual" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="0">
-    <oddHeader/>
-    <oddFooter>&amp;L13 Haftalık Nakit Akışı ve Ödeme Planlama Sistemi — PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:AN21"/>
@@ -10115,7 +7476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10313,7 +7674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10519,7 +7880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10687,7 +8048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10907,7 +8268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10980,7 +8341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11158,253 +8519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" style="57" min="1" max="1"/>
-    <col width="30" customWidth="1" style="57" min="2" max="2"/>
-    <col width="18" customWidth="1" style="57" min="3" max="3"/>
-    <col width="10" customWidth="1" style="57" min="4" max="4"/>
-    <col width="12" customWidth="1" style="57" min="5" max="5"/>
-    <col width="12" customWidth="1" style="57" min="6" max="6"/>
-    <col width="35" customWidth="1" style="57" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="76" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="77" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="77" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="77" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="77" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="77" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="77" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="78" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="79" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="80" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="78" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="79" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="70" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="80" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="78" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="79" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="70" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="80" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="78" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="79" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="70" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="80" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="78" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="79" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="80" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="78" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="79" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="80" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12404,7 +9519,485 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="16" customWidth="1" style="57" min="3" max="3"/>
+    <col width="32" customWidth="1" style="57" min="4" max="4"/>
+    <col width="18" customWidth="1" style="57" min="5" max="5"/>
+    <col width="12" customWidth="1" style="57" min="6" max="6"/>
+    <col width="18" customWidth="1" style="57" min="7" max="7"/>
+    <col width="22" customWidth="1" style="57" min="8" max="8"/>
+    <col width="16" customWidth="1" style="57" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="180" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="181" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="182" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="183" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="183" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="183" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="183" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="183" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="183" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="183" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="183" t="inlineStr">
+        <is>
+          <t>DURUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="184" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="185" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="186" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="187" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="189">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="186" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="190" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="191" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="192" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="193" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="194" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="196">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="193" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="197" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="184" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="185" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="186" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="187" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="188" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="189">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="186" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="190" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="191" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="192" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="193" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="194" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="196">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="193" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="198" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="184" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="185" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="186" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="187" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="189">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="186" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="190" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="191" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="192" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="193" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="194" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="196">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="193" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="199" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="184" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="185" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="186" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="187" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="189">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="186" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="190" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="191" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="192" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="193" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="194" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="196">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="193" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="198" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="184" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="185" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="186" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="187" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="188" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="189">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="186" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="190" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="191" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="192" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="193" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="194" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="195" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="196">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="193" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="198" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="200" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="168" t="n"/>
+      <c r="D17" s="168" t="n"/>
+      <c r="E17" s="201">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="168" t="n"/>
+      <c r="G17" s="168" t="n"/>
+      <c r="H17" s="168" t="n"/>
+      <c r="I17" s="168" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12691,81 +10284,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="57" min="1" max="1"/>
-    <col width="25" customWidth="1" style="57" min="2" max="2"/>
-    <col width="20" customWidth="1" style="57" min="3" max="3"/>
-    <col width="20" customWidth="1" style="57" min="4" max="4"/>
-    <col width="15" customWidth="1" style="57" min="5" max="5"/>
-    <col width="25" customWidth="1" style="57" min="6" max="6"/>
-    <col width="15" customWidth="1" style="57" min="7" max="7"/>
-    <col width="15" customWidth="1" style="57" min="8" max="8"/>
+    <col width="3" customWidth="1" style="57" min="1" max="1"/>
+    <col width="24" customWidth="1" style="57" min="2" max="2"/>
+    <col width="15" customWidth="1" style="57" min="3" max="3"/>
+    <col width="15" customWidth="1" style="57" min="4" max="4"/>
+    <col width="22" customWidth="1" style="57" min="5" max="5"/>
+    <col width="6" customWidth="1" style="57" min="6" max="6"/>
+    <col width="6" customWidth="1" style="57" min="7" max="7"/>
+    <col width="24" customWidth="1" style="57" min="8" max="8"/>
+    <col width="15" customWidth="1" style="57" min="9" max="9"/>
+    <col width="15" customWidth="1" style="57" min="10" max="10"/>
+    <col width="22" customWidth="1" style="57" min="11" max="11"/>
+    <col width="6" customWidth="1" style="57" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="76" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="81" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="202" t="inlineStr">
+        <is>
+          <t>13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="203" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="204" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="82" t="inlineStr">
-        <is>
-          <t>Şirket likidite ve marj açısından üst çeyrekte yer almaktadır. Denetim motoru sıfır açık ve sıfır hata doğrulamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="205" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="143" t="n"/>
+      <c r="D6" s="143" t="n"/>
+      <c r="E6" s="143" t="n"/>
+      <c r="F6" s="143" t="n"/>
+      <c r="H6" s="206" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="143" t="n"/>
+      <c r="J6" s="143" t="n"/>
+      <c r="K6" s="143" t="n"/>
+      <c r="L6" s="143" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="143" t="n"/>
+      <c r="C7" s="143" t="n"/>
+      <c r="D7" s="143" t="n"/>
+      <c r="E7" s="143" t="n"/>
+      <c r="F7" s="143" t="n"/>
+      <c r="H7" s="143" t="n"/>
+      <c r="I7" s="143" t="n"/>
+      <c r="J7" s="143" t="n"/>
+      <c r="K7" s="143" t="n"/>
+      <c r="L7" s="143" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="207" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="143" t="n"/>
+      <c r="D8" s="143" t="n"/>
+      <c r="E8" s="208" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="143" t="n"/>
+      <c r="H8" s="207" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="143" t="n"/>
+      <c r="J8" s="143" t="n"/>
+      <c r="K8" s="209" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="143" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="81" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="207" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="143" t="n"/>
+      <c r="D9" s="143" t="n"/>
+      <c r="E9" s="210" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="n"/>
+      <c r="H9" s="207" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="143" t="n"/>
+      <c r="J9" s="143" t="n"/>
+      <c r="K9" s="210" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="143" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="82" t="inlineStr">
-        <is>
-          <t>Ters Stres Senaryosu: Satışlar %30 düşse bile şirket 180 gün dış finansman olmaksızın nakit pozitif kalabilmektedir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="207" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="143" t="n"/>
+      <c r="D10" s="143" t="n"/>
+      <c r="E10" s="211" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="143" t="n"/>
+      <c r="H10" s="207" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="143" t="n"/>
+      <c r="J10" s="143" t="n"/>
+      <c r="K10" s="211" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="143" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="207" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="143" t="n"/>
+      <c r="D11" s="143" t="n"/>
+      <c r="E11" s="211" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="143" t="n"/>
+      <c r="H11" s="207" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="143" t="n"/>
+      <c r="J11" s="143" t="n"/>
+      <c r="K11" s="211" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="143" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="143" t="n"/>
+      <c r="C12" s="143" t="n"/>
+      <c r="D12" s="143" t="n"/>
+      <c r="E12" s="143" t="n"/>
+      <c r="F12" s="143" t="n"/>
+      <c r="H12" s="143" t="n"/>
+      <c r="I12" s="143" t="n"/>
+      <c r="J12" s="143" t="n"/>
+      <c r="K12" s="143" t="n"/>
+      <c r="L12" s="143" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="81" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="143" t="n"/>
+      <c r="C13" s="143" t="n"/>
+      <c r="D13" s="143" t="n"/>
+      <c r="E13" s="143" t="n"/>
+      <c r="F13" s="143" t="n"/>
+      <c r="H13" s="143" t="n"/>
+      <c r="I13" s="143" t="n"/>
+      <c r="J13" s="143" t="n"/>
+      <c r="K13" s="143" t="n"/>
+      <c r="L13" s="143" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="212" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="143" t="n"/>
+      <c r="D14" s="143" t="n"/>
+      <c r="E14" s="143" t="n"/>
+      <c r="F14" s="143" t="n"/>
+      <c r="H14" s="213" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="143" t="n"/>
+      <c r="J14" s="143" t="n"/>
+      <c r="K14" s="143" t="n"/>
+      <c r="L14" s="143" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="78" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="78" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="143" t="n"/>
+      <c r="C15" s="143" t="n"/>
+      <c r="D15" s="143" t="n"/>
+      <c r="E15" s="143" t="n"/>
+      <c r="F15" s="143" t="n"/>
+      <c r="H15" s="143" t="n"/>
+      <c r="I15" s="143" t="n"/>
+      <c r="J15" s="143" t="n"/>
+      <c r="K15" s="143" t="n"/>
+      <c r="L15" s="143" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="170" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="170" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="170" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="170" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
@@ -111,13 +111,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;₺ &quot;#,##0;[RED]&quot;(₺ &quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;[RED]\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="96">
     <font>
@@ -1275,7 +1276,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1904,6 +1905,24 @@
     </xf>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="58" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="59" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="62" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="81" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="51" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="78" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="78" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -12007,7 +12026,7 @@
     <col width="6" customWidth="1" style="57" min="7" max="7"/>
     <col width="24" customWidth="1" style="57" min="8" max="8"/>
     <col width="15" customWidth="1" style="57" min="9" max="9"/>
-    <col width="14" customWidth="1" style="57" min="10" max="10"/>
+    <col width="15" customWidth="1" style="57" min="10" max="10"/>
     <col width="12" customWidth="1" style="57" min="11" max="11"/>
     <col width="18" customWidth="1" style="57" min="12" max="12"/>
     <col width="18" customWidth="1" style="57" min="13" max="13"/>
@@ -12023,7 +12042,7 @@
     <row r="2">
       <c r="B2" s="138" t="inlineStr">
         <is>
-          <t>13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
+          <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI</t>
         </is>
       </c>
       <c r="L2" s="139" t="inlineStr">
@@ -12040,7 +12059,7 @@
     <row r="3">
       <c r="B3" s="141" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: KOBİ sahipleri, finans yöneticileri, muhasebe sorumluları, mali müşavirler · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
@@ -12105,31 +12124,27 @@
       <c r="M6" s="143" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="152" t="inlineStr">
-        <is>
-          <t>₺34.850.000</t>
-        </is>
+      <c r="B7" s="239">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="143" t="n"/>
       <c r="D7" s="143" t="n"/>
-      <c r="E7" s="153" t="inlineStr">
-        <is>
-          <t>₺2.480.000</t>
-        </is>
+      <c r="E7" s="240">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="143" t="n"/>
       <c r="G7" s="143" t="n"/>
-      <c r="H7" s="152" t="inlineStr">
-        <is>
-          <t>₺18.420.000</t>
-        </is>
+      <c r="H7" s="239">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="143" t="n"/>
       <c r="J7" s="143" t="n"/>
-      <c r="K7" s="154" t="inlineStr">
-        <is>
-          <t>2.14x</t>
-        </is>
+      <c r="K7" s="154">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="143" t="n"/>
       <c r="M7" s="143" t="n"/>
@@ -12151,7 +12166,7 @@
     <row r="9">
       <c r="B9" s="155" t="inlineStr">
         <is>
-          <t>↑ %14.2 konsolide vadesiz + fon</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="143" t="n"/>
@@ -12165,14 +12180,14 @@
       <c r="G9" s="143" t="n"/>
       <c r="H9" s="155" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %52.8 ORAN</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="143" t="n"/>
       <c r="J9" s="143" t="n"/>
       <c r="K9" s="157" t="inlineStr">
         <is>
-          <t>✓ İDEAL borç servis karşılama</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="143" t="n"/>
@@ -12181,7 +12196,7 @@
     <row r="11">
       <c r="B11" s="81" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="158" t="inlineStr">
@@ -12198,7 +12213,7 @@
     <row r="12">
       <c r="B12" s="80" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="80" t="inlineStr">
@@ -12271,18 +12286,16 @@
       </c>
       <c r="H15" s="161" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="161" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="162" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="241">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="242">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="163" t="inlineStr">
         <is>
@@ -12312,18 +12325,16 @@
       </c>
       <c r="H16" s="161" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="161" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="162" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="241">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="242">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="163" t="inlineStr">
         <is>
@@ -12353,18 +12364,16 @@
       </c>
       <c r="H17" s="161" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="161" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="162" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="241">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="242">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="163" t="inlineStr">
         <is>
@@ -12394,18 +12403,16 @@
       </c>
       <c r="H18" s="161" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="161" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="162" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="241">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="242">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="163" t="inlineStr">
         <is>
@@ -12438,15 +12445,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="166" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="167" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="243">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="244">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="168" t="inlineStr"/>
       <c r="L19" s="169" t="inlineStr">
@@ -12532,7 +12537,7 @@
       </c>
       <c r="K24" s="175" t="inlineStr">
         <is>
-          <t>Atıl kalan ₺4.2M nakit rezervinin gecelik repoda değerlendirilmesiyle ek getiri.</t>
+          <t>Atıl kalan nakit rezervinin değerlendirilmesiyle ek finansal getiri imkanı.</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14738,7 @@
     <row r="3">
       <c r="B3" s="180" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="181" t="inlineStr">
@@ -14802,10 +14807,10 @@
       </c>
       <c r="D6" s="186" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="187" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="245" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="188" t="n">
@@ -14839,10 +14844,10 @@
       </c>
       <c r="D7" s="193" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="194" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="245" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="195" t="n">
@@ -14876,10 +14881,10 @@
       </c>
       <c r="D8" s="186" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="187" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="245" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="188" t="n">
@@ -14913,10 +14918,10 @@
       </c>
       <c r="D9" s="193" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="194" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="245" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="195" t="n">
@@ -14950,10 +14955,10 @@
       </c>
       <c r="D10" s="186" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="187" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="245" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="188" t="n">
@@ -14987,10 +14992,10 @@
       </c>
       <c r="D11" s="193" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="194" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="245" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="195" t="n">
@@ -15002,7 +15007,7 @@
       </c>
       <c r="H11" s="193" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="199" t="inlineStr">
@@ -15024,10 +15029,10 @@
       </c>
       <c r="D12" s="186" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="187" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="245" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="188" t="n">
@@ -15039,7 +15044,7 @@
       </c>
       <c r="H12" s="186" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="190" t="inlineStr">
@@ -15061,10 +15066,10 @@
       </c>
       <c r="D13" s="193" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="194" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="245" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="195" t="n">
@@ -15098,10 +15103,10 @@
       </c>
       <c r="D14" s="186" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="187" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="245" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="188" t="n">
@@ -15135,10 +15140,10 @@
       </c>
       <c r="D15" s="193" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="194" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="245" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="195" t="n">
@@ -15222,14 +15227,14 @@
     <row r="2">
       <c r="B2" s="202" t="inlineStr">
         <is>
-          <t>13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="203" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, finans yöneticileri, muhasebe sorumluları, mali müşavirler</t>
         </is>
       </c>
     </row>
@@ -15308,10 +15313,9 @@
       </c>
       <c r="C9" s="143" t="n"/>
       <c r="D9" s="143" t="n"/>
-      <c r="E9" s="210" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="246">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="143" t="n"/>
       <c r="H9" s="207" t="inlineStr">
@@ -15321,10 +15325,9 @@
       </c>
       <c r="I9" s="143" t="n"/>
       <c r="J9" s="143" t="n"/>
-      <c r="K9" s="210" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="246">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="143" t="n"/>
     </row>
@@ -15336,10 +15339,9 @@
       </c>
       <c r="C10" s="143" t="n"/>
       <c r="D10" s="143" t="n"/>
-      <c r="E10" s="211" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="247">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="143" t="n"/>
       <c r="H10" s="207" t="inlineStr">
@@ -15349,10 +15351,9 @@
       </c>
       <c r="I10" s="143" t="n"/>
       <c r="J10" s="143" t="n"/>
-      <c r="K10" s="211" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="247">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="143" t="n"/>
     </row>
@@ -15364,10 +15365,9 @@
       </c>
       <c r="C11" s="143" t="n"/>
       <c r="D11" s="143" t="n"/>
-      <c r="E11" s="211" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="248">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="143" t="n"/>
       <c r="H11" s="207" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
@@ -120,7 +120,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="96">
+  <fonts count="98">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -715,8 +715,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -900,6 +912,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1276,7 +1294,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1923,6 +1941,30 @@
     </xf>
     <xf numFmtId="170" fontId="78" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6433,20 +6475,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="57" min="1" max="1"/>
-    <col width="78" customWidth="1" style="57" min="2" max="2"/>
+    <col width="147.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="215" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="216" t="inlineStr">
         <is>
@@ -6711,6 +6770,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="57">
       <c r="A26" s="219" t="inlineStr">
         <is>
@@ -6809,7 +6869,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6824,8 +6884,16 @@
   <dimension ref="A1:AN25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="90" customWidth="1" style="83" min="1" max="1"/>
+    <col width="105.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="14" customWidth="1" style="83" min="2" max="10"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="57">
@@ -6835,6 +6903,9 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="57">
       <c r="A5" s="85" t="inlineStr">
         <is>
@@ -6849,6 +6920,8 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="87" t="inlineStr">
         <is>
@@ -6884,6 +6957,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="87" t="inlineStr">
         <is>
@@ -6898,6 +6972,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="87" t="inlineStr">
         <is>
@@ -6926,6 +7001,9 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="89" t="inlineStr">
         <is>
@@ -6953,17 +7031,36 @@
   <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="90" customWidth="1" style="83" min="1" max="1"/>
+    <col width="211.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="14" customWidth="1" style="83" min="2" max="10"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="19.5" customHeight="1" s="57">
       <c r="A5" s="90" t="inlineStr">
         <is>
@@ -6971,6 +7068,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="87" t="inlineStr">
         <is>
@@ -7016,6 +7114,9 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="57"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="87" t="inlineStr">
         <is>
@@ -7050,7 +7151,7 @@
     <mergeCell ref="A8:BH9"/>
     <mergeCell ref="A11:BH12"/>
     <mergeCell ref="A14:BH15"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7067,30 +7168,40 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="83" min="1" max="1"/>
-    <col width="14" customWidth="1" style="83" min="2" max="2"/>
-    <col width="12" customWidth="1" style="83" min="3" max="3"/>
-    <col width="18" customWidth="1" style="83" min="4" max="4"/>
+    <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="23.5" customWidth="1" style="83" min="2" max="2"/>
+    <col width="12.5" customWidth="1" style="83" min="3" max="3"/>
+    <col width="21.5" customWidth="1" style="83" min="4" max="4"/>
     <col width="14" customWidth="1" style="83" min="5" max="5"/>
     <col width="12" customWidth="1" style="83" min="6" max="6"/>
     <col width="14" customWidth="1" style="83" min="7" max="7"/>
-    <col width="40" customWidth="1" style="83" min="8" max="8"/>
+    <col width="44.5" customWidth="1" style="83" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>NAKIT GIRISLERI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="180" customHeight="1" s="57">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>13 HAFTALIK NAKİT GİRİŞ PLANI — beklenen tahsilat, satış ve finansman kaynaklarını girin.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -8101,8 +8212,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="C6:C5000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="10" text="" percent="0" bottom="0">
@@ -8181,29 +8293,40 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="83" min="1" max="1"/>
-    <col width="14" customWidth="1" style="83" min="2" max="2"/>
+    <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="23.5" customWidth="1" style="83" min="2" max="2"/>
     <col width="18" customWidth="1" style="83" min="3" max="3"/>
     <col width="14" customWidth="1" style="83" min="4" max="5"/>
+    <col width="13.5" customWidth="1" style="57" min="5" max="5"/>
     <col width="12" customWidth="1" style="83" min="6" max="6"/>
     <col width="14" customWidth="1" style="83" min="7" max="7"/>
     <col width="40" customWidth="1" style="83" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>NAKIT CIKISLARI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="135.75" customHeight="1" s="57">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>13 HAFTALIK NAKİT ÇIKIŞ PLANI — ödenmesi planlanan giderleri girin.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -9052,8 +9175,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D5000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
@@ -9129,23 +9253,38 @@
   <dimension ref="A1:AN35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="11" customWidth="1" style="83" min="1" max="1"/>
-    <col width="15" customWidth="1" style="83" min="2" max="5"/>
+    <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="20.5" customWidth="1" style="83" min="2" max="5"/>
+    <col width="16.5" customWidth="1" style="57" min="3" max="3"/>
+    <col width="16.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="16.5" customWidth="1" style="57" min="5" max="5"/>
     <col width="13" customWidth="1" style="83" min="6" max="6"/>
-    <col width="17" customWidth="1" style="83" min="7" max="8"/>
+    <col width="21.5" customWidth="1" style="83" min="7" max="8"/>
+    <col width="21.5" customWidth="1" style="57" min="8" max="8"/>
     <col width="15" customWidth="1" style="83" min="9" max="9"/>
     <col width="42" customWidth="1" style="83" min="10" max="10"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>HAFTALIK PLAN — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="135.75" customHeight="1" s="57">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+      <c r="J1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>HAFTA HAFTA NAKİT AKIŞI — giriş ve çıkış planlarından otomatik toplanır.</t>
         </is>
@@ -9156,6 +9295,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -10438,8 +10578,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:F1000">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="12" text="" percent="0" bottom="0">
@@ -10494,17 +10635,31 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="44" customWidth="1" style="83" min="1" max="1"/>
-    <col width="28" customWidth="1" style="83" min="2" max="2"/>
+    <col width="55.5" customWidth="1" style="83" min="2" max="2"/>
     <col width="95" customWidth="1" style="83" min="3" max="3"/>
     <col width="18" customWidth="1" style="83" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>MOTOR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="57">
       <c r="A2" s="108" t="inlineStr">
@@ -10513,6 +10668,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="109" t="inlineStr">
         <is>
@@ -10751,6 +10907,8 @@
         <v/>
       </c>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="110" t="inlineStr">
         <is>
@@ -10828,6 +10986,8 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37" ht="15" customHeight="1" s="57">
       <c r="A37" s="109" t="inlineStr">
         <is>
@@ -11075,6 +11235,7 @@
         <v/>
       </c>
     </row>
+    <row r="54"/>
     <row r="55" ht="19.5" customHeight="1" s="57">
       <c r="A55" s="108" t="inlineStr">
         <is>
@@ -11085,7 +11246,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A55:AN55"/>
     <mergeCell ref="A2:AN2"/>
   </mergeCells>
@@ -11107,22 +11268,43 @@
   <cols>
     <col width="34" customWidth="1" style="83" min="1" max="1"/>
     <col width="22" customWidth="1" style="83" min="2" max="2"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>KONTROLLER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+      <c r="J1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>VERİ KALİTESİ VE SİSTEM SAĞLIĞI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="116" t="inlineStr">
         <is>
@@ -11255,6 +11437,10 @@
         <v/>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="36.75" customHeight="1" s="57">
       <c r="A22" s="103" t="inlineStr">
         <is>
@@ -11264,8 +11450,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
@@ -11316,24 +11503,42 @@
   <dimension ref="A1:AN23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="36" customWidth="1" style="83" min="1" max="1"/>
-    <col width="60" customWidth="1" style="83" min="2" max="2"/>
+    <col width="190.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="88.5" customWidth="1" style="83" min="2" max="2"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>KARAR MOTORU — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="52.5" customHeight="1" s="57">
-      <c r="A3" s="121" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>KARAR MOTORU — hangi hafta para bitecek, hangi önlem alınmalı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="119" t="inlineStr">
         <is>
@@ -11488,6 +11693,10 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23" ht="60.75" customHeight="1" s="57">
       <c r="A23" s="103" t="inlineStr">
         <is>
@@ -11497,8 +11706,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThan" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
@@ -11558,25 +11768,42 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="34" customWidth="1" style="83" min="1" max="1"/>
-    <col width="18" customWidth="1" style="83" min="2" max="3"/>
+    <col width="159.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="22.5" customWidth="1" style="83" min="2" max="3"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
     <col width="20" customWidth="1" style="83" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>SENARYO DUYARLILIK — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>SENARYO VE DUYARLILIK ANALİZİ</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="119" t="inlineStr">
         <is>
@@ -11662,6 +11889,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="125" t="inlineStr">
         <is>
@@ -11767,6 +11995,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="48.75" customHeight="1" s="57">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -11776,8 +12005,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="lessThan" aboveAverage="0" dxfId="13" text="" percent="0" bottom="0">
@@ -11818,19 +12048,36 @@
   <dimension ref="A1:AN21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="44" customWidth="1" style="83" min="1" max="1"/>
+    <col width="98.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="30" customWidth="1" style="83" min="2" max="2"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>RAPOR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1" s="57">
-      <c r="A3" s="90" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>YÖNETİCİ NAKİT AKIŞ RAPORU</t>
         </is>
@@ -11869,6 +12116,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="125" t="inlineStr">
         <is>
@@ -11981,6 +12229,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="24.75" customHeight="1" s="57">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -11990,8 +12239,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.5"/>
@@ -12014,22 +12264,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
-    <col width="18" customWidth="1" style="57" min="2" max="2"/>
+    <col width="84.5" customWidth="1" style="57" min="2" max="2"/>
     <col width="15" customWidth="1" style="57" min="3" max="3"/>
-    <col width="12" customWidth="1" style="57" min="4" max="4"/>
-    <col width="16" customWidth="1" style="57" min="5" max="5"/>
+    <col width="15.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="36.5" customWidth="1" style="57" min="5" max="5"/>
     <col width="18" customWidth="1" style="57" min="6" max="6"/>
-    <col width="6" customWidth="1" style="57" min="7" max="7"/>
-    <col width="24" customWidth="1" style="57" min="8" max="8"/>
+    <col width="15.5" customWidth="1" style="57" min="7" max="7"/>
+    <col width="75.5" customWidth="1" style="57" min="8" max="8"/>
     <col width="15" customWidth="1" style="57" min="9" max="9"/>
-    <col width="15" customWidth="1" style="57" min="10" max="10"/>
-    <col width="12" customWidth="1" style="57" min="11" max="11"/>
+    <col width="15.5" customWidth="1" style="57" min="10" max="10"/>
+    <col width="79.5" customWidth="1" style="57" min="11" max="11"/>
     <col width="18" customWidth="1" style="57" min="12" max="12"/>
     <col width="18" customWidth="1" style="57" min="13" max="13"/>
+    <col width="13" customWidth="1" style="57" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12063,6 +12314,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="142" t="inlineStr">
         <is>
@@ -12193,6 +12445,7 @@
       <c r="L9" s="143" t="n"/>
       <c r="M9" s="143" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="81" t="inlineStr">
         <is>
@@ -12222,6 +12475,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="159" t="inlineStr">
         <is>
@@ -12476,6 +12730,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="170" t="inlineStr">
         <is>
@@ -12564,13 +12819,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="251" t="n"/>
+      <c r="H26" s="251" t="n"/>
+      <c r="I26" s="252" t="n"/>
       <c r="K26" s="179" t="inlineStr">
         <is>
           <t>FONLAMA SENARYOSUNU İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="253" t="n"/>
+      <c r="G27" s="254" t="n"/>
+      <c r="H27" s="254" t="n"/>
+      <c r="I27" s="255" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -12590,27 +12853,42 @@
   <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="10" customWidth="1" style="83" min="1" max="1"/>
+    <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="12" customWidth="1" style="83" min="2" max="2"/>
     <col width="14" customWidth="1" style="83" min="3" max="3"/>
-    <col width="18" customWidth="1" style="83" min="4" max="4"/>
-    <col width="20" customWidth="1" style="83" min="5" max="5"/>
+    <col width="19.5" customWidth="1" style="83" min="4" max="4"/>
+    <col width="21.5" customWidth="1" style="83" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>ORNEK VERI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="90.75" customHeight="1" s="57">
-      <c r="A3" s="93" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>ÖRNEK VERİ — otomasyon ve içe aktarma için yapı</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -12778,8 +13056,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12796,25 +13075,42 @@
   <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="40" customWidth="1" style="83" min="1" max="1"/>
+    <col width="96.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="20" customWidth="1" style="83" min="2" max="2"/>
     <col width="18" customWidth="1" style="83" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>TESTLER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>SİSTEM TESTLERİ VE DENETİM KAYDI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -12937,6 +13233,9 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16" ht="24.75" customHeight="1" s="57">
       <c r="A16" s="103" t="inlineStr">
         <is>
@@ -12946,8 +13245,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12961,24 +13261,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="12" customWidth="1" style="83" min="1" max="1"/>
+    <col width="16.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="16" customWidth="1" style="83" min="2" max="2"/>
     <col width="14" customWidth="1" style="83" min="3" max="4"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
     <col width="10" customWidth="1" style="83" min="5" max="5"/>
-    <col width="14" customWidth="1" style="83" min="6" max="6"/>
-    <col width="40" customWidth="1" style="83" min="7" max="7"/>
+    <col width="16.5" customWidth="1" style="83" min="6" max="6"/>
+    <col width="40.5" customWidth="1" style="83" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="57">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>AKIS — OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="83" t="inlineStr">
         <is>
@@ -13156,6 +13469,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="83" t="inlineStr">
         <is>
@@ -13169,6 +13483,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -13185,24 +13502,41 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="83" min="1" max="1"/>
-    <col width="14" customWidth="1" style="83" min="2" max="2"/>
-    <col width="80" customWidth="1" style="83" min="3" max="3"/>
+    <col width="14.5" customWidth="1" style="83" min="2" max="2"/>
+    <col width="84.5" customWidth="1" style="83" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>DEGISIKLIK KAYDI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>DEGİŞİKLİK KAYDI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -13239,8 +13573,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13258,25 +13593,41 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="83" min="1" max="1"/>
-    <col width="20" customWidth="1" style="83" min="3" max="3"/>
-    <col width="16" customWidth="1" style="83" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="2" max="2"/>
+    <col width="21.5" customWidth="1" style="83" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="17.5" customWidth="1" style="83" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
     <col width="18" customWidth="1" style="83" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>LISTELER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>AÇILIR LİSTE KAYNAKLARI</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="106" t="inlineStr">
         <is>
@@ -13417,8 +13768,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AN1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13435,12 +13787,15 @@
   <dimension ref="A1:AN38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="30" customWidth="1" style="83" min="1" max="1"/>
+    <col width="31.5" customWidth="1" style="83" min="1" max="1"/>
     <col width="42" customWidth="1" style="83" min="2" max="2"/>
     <col width="12" customWidth="1" style="83" min="3" max="3"/>
     <col width="56" customWidth="1" style="83" min="4" max="4"/>
-    <col width="20" customWidth="1" style="83" min="5" max="5"/>
+    <col width="20.5" customWidth="1" style="83" min="5" max="5"/>
     <col width="14" customWidth="1" style="83" min="6" max="7"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
     <col width="16" customWidth="1" style="83" min="10" max="10"/>
     <col width="13" customWidth="1" style="83" min="11" max="11"/>
     <col width="28" customWidth="1" style="83" min="12" max="12"/>
@@ -13448,12 +13803,20 @@
     <col width="13" customWidth="1" style="83" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>AYARLAR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="57">
       <c r="A2" s="108" t="inlineStr">
@@ -13462,6 +13825,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="109" t="inlineStr">
         <is>
@@ -13569,6 +13933,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="109" t="inlineStr">
         <is>
@@ -14278,6 +14643,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="57">
       <c r="J34" s="83" t="inlineStr">
         <is>
@@ -14416,7 +14782,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:AN2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -14435,23 +14801,42 @@
   <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="80" customWidth="1" style="83" min="1" max="1"/>
+    <col width="127.5" customWidth="1" style="83" min="1" max="1"/>
+    <col width="13" customWidth="1" style="57" min="2" max="2"/>
+    <col width="13" customWidth="1" style="57" min="3" max="3"/>
+    <col width="13" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="57">
-      <c r="A1" s="84" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>KILAVUZ — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="57">
-      <c r="A3" s="115" t="inlineStr">
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1" s="57">
+      <c r="A3" s="268" t="inlineStr">
         <is>
           <t>KULLANIM KILAVUZU</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="125" t="inlineStr">
         <is>
@@ -14578,6 +14963,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="125" t="inlineStr">
         <is>
@@ -14613,6 +14999,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="125" t="inlineStr">
         <is>
@@ -14641,6 +15028,8 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="57">
       <c r="A36" s="125" t="inlineStr">
         <is>
@@ -14678,7 +15067,8 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:BH6"/>
     <mergeCell ref="A25:BH25"/>
     <mergeCell ref="A16:BH16"/>
@@ -14692,11 +15082,11 @@
     <mergeCell ref="A32:BH32"/>
     <mergeCell ref="A8:BH8"/>
     <mergeCell ref="A22:BH22"/>
-    <mergeCell ref="A1:AN1"/>
     <mergeCell ref="A20:BH20"/>
     <mergeCell ref="A38:BH38"/>
     <mergeCell ref="A10:BH10"/>
     <mergeCell ref="A28:BH28"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A31:BH31"/>
     <mergeCell ref="A40:BH40"/>
     <mergeCell ref="A39:BH39"/>
@@ -14714,18 +15104,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
-    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="36.5" customWidth="1" style="57" min="2" max="2"/>
     <col width="16" customWidth="1" style="57" min="3" max="3"/>
-    <col width="32" customWidth="1" style="57" min="4" max="4"/>
-    <col width="18" customWidth="1" style="57" min="5" max="5"/>
-    <col width="12" customWidth="1" style="57" min="6" max="6"/>
+    <col width="37.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="18.5" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13.5" customWidth="1" style="57" min="6" max="6"/>
     <col width="18" customWidth="1" style="57" min="7" max="7"/>
-    <col width="22" customWidth="1" style="57" min="8" max="8"/>
+    <col width="22.5" customWidth="1" style="57" min="8" max="8"/>
     <col width="16" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14735,12 +15126,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="180" t="inlineStr">
         <is>
           <t>🔍  13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="256" t="n"/>
+      <c r="D3" s="256" t="n"/>
+      <c r="E3" s="257" t="n"/>
       <c r="G3" s="181" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -14752,6 +15147,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="183" t="inlineStr">
         <is>
@@ -15164,22 +15560,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="200" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="168" t="n"/>
-      <c r="D17" s="168" t="n"/>
       <c r="E17" s="201">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="168" t="n"/>
-      <c r="G17" s="168" t="n"/>
-      <c r="H17" s="168" t="n"/>
-      <c r="I17" s="168" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -15200,7 +15591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
@@ -15245,25 +15636,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="205" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="143" t="n"/>
-      <c r="D6" s="143" t="n"/>
-      <c r="E6" s="143" t="n"/>
-      <c r="F6" s="143" t="n"/>
+      <c r="C6" s="256" t="n"/>
+      <c r="D6" s="256" t="n"/>
+      <c r="E6" s="256" t="n"/>
+      <c r="F6" s="257" t="n"/>
       <c r="H6" s="206" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="143" t="n"/>
-      <c r="J6" s="143" t="n"/>
-      <c r="K6" s="143" t="n"/>
-      <c r="L6" s="143" t="n"/>
+      <c r="I6" s="256" t="n"/>
+      <c r="J6" s="256" t="n"/>
+      <c r="K6" s="256" t="n"/>
+      <c r="L6" s="257" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="143" t="n"/>
@@ -15414,32 +15806,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="143" t="n"/>
-      <c r="D14" s="143" t="n"/>
-      <c r="E14" s="143" t="n"/>
-      <c r="F14" s="143" t="n"/>
+      <c r="C14" s="258" t="n"/>
+      <c r="D14" s="258" t="n"/>
+      <c r="E14" s="258" t="n"/>
+      <c r="F14" s="259" t="n"/>
       <c r="H14" s="213" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="143" t="n"/>
-      <c r="J14" s="143" t="n"/>
-      <c r="K14" s="143" t="n"/>
-      <c r="L14" s="143" t="n"/>
+      <c r="I14" s="260" t="n"/>
+      <c r="J14" s="260" t="n"/>
+      <c r="K14" s="260" t="n"/>
+      <c r="L14" s="261" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="143" t="n"/>
-      <c r="C15" s="143" t="n"/>
-      <c r="D15" s="143" t="n"/>
-      <c r="E15" s="143" t="n"/>
-      <c r="F15" s="143" t="n"/>
-      <c r="H15" s="143" t="n"/>
-      <c r="I15" s="143" t="n"/>
-      <c r="J15" s="143" t="n"/>
-      <c r="K15" s="143" t="n"/>
-      <c r="L15" s="143" t="n"/>
-    </row>
+      <c r="B15" s="262" t="n"/>
+      <c r="C15" s="263" t="n"/>
+      <c r="D15" s="263" t="n"/>
+      <c r="E15" s="263" t="n"/>
+      <c r="F15" s="264" t="n"/>
+      <c r="H15" s="265" t="n"/>
+      <c r="I15" s="266" t="n"/>
+      <c r="J15" s="266" t="n"/>
+      <c r="K15" s="266" t="n"/>
+      <c r="L15" s="267" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="68" t="inlineStr">
         <is>
@@ -15447,6 +15840,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="170" t="inlineStr">
         <is>
@@ -15521,25 +15915,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
-    <col width="24" customWidth="1" style="57" min="2" max="2"/>
-    <col width="22" customWidth="1" style="57" min="3" max="3"/>
-    <col width="27" customWidth="1" style="57" min="4" max="4"/>
-    <col width="29" customWidth="1" style="57" min="5" max="5"/>
-    <col width="20" customWidth="1" style="57" min="6" max="6"/>
+    <col width="30.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="23.5" customWidth="1" style="57" min="3" max="3"/>
+    <col width="48.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="43.5" customWidth="1" style="57" min="5" max="5"/>
+    <col width="21.5" customWidth="1" style="57" min="6" max="6"/>
     <col width="21" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="220" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="221" t="inlineStr">
         <is>
@@ -15999,7 +16405,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16012,22 +16418,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="57" min="1" max="1"/>
-    <col width="52" customWidth="1" style="57" min="2" max="2"/>
-    <col width="34" customWidth="1" style="57" min="3" max="3"/>
+    <col width="89.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="34.5" customWidth="1" style="57" min="3" max="3"/>
     <col width="16" customWidth="1" style="57" min="4" max="4"/>
+    <col width="13" customWidth="1" style="57" min="5" max="5"/>
+    <col width="13" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="223" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="224" t="inlineStr">
         <is>
@@ -16739,7 +17160,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16752,24 +17173,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="57" min="1" max="1"/>
-    <col width="36" customWidth="1" style="57" min="2" max="2"/>
-    <col width="48" customWidth="1" style="57" min="3" max="3"/>
-    <col width="34" customWidth="1" style="57" min="4" max="4"/>
-    <col width="30" customWidth="1" style="57" min="5" max="5"/>
+    <col width="30.5" customWidth="1" style="57" min="1" max="1"/>
+    <col width="71.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="160.5" customWidth="1" style="57" min="3" max="3"/>
+    <col width="70.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="50.5" customWidth="1" style="57" min="5" max="5"/>
     <col width="16" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="228" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="229" t="inlineStr">
         <is>
@@ -17412,7 +17846,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17425,24 +17859,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="57" min="1" max="1"/>
-    <col width="40" customWidth="1" style="57" min="2" max="2"/>
-    <col width="50" customWidth="1" style="57" min="3" max="3"/>
-    <col width="30" customWidth="1" style="57" min="4" max="4"/>
-    <col width="28" customWidth="1" style="57" min="5" max="5"/>
-    <col width="26" customWidth="1" style="57" min="6" max="6"/>
+    <col width="22.5" customWidth="1" style="57" min="1" max="1"/>
+    <col width="60.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="57" min="3" max="3"/>
+    <col width="40.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="39.5" customWidth="1" style="57" min="5" max="5"/>
+    <col width="27.5" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="232" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -17957,7 +18404,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17970,23 +18417,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="57" min="1" max="1"/>
-    <col width="32" customWidth="1" style="57" min="2" max="2"/>
-    <col width="54" customWidth="1" style="57" min="3" max="3"/>
-    <col width="34" customWidth="1" style="57" min="4" max="4"/>
+    <col width="20.5" customWidth="1" style="57" min="1" max="1"/>
+    <col width="41.5" customWidth="1" style="57" min="2" max="2"/>
+    <col width="86.5" customWidth="1" style="57" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="57" min="4" max="4"/>
+    <col width="33.5" customWidth="1" style="57" min="5" max="5"/>
     <col width="16" customWidth="1" style="57" min="6" max="6"/>
+    <col width="13" customWidth="1" style="57" min="7" max="7"/>
+    <col width="13" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="13" customWidth="1" style="57" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="57">
-      <c r="A1" s="235" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="57">
+      <c r="A1" s="249" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="250" t="n"/>
+      <c r="C1" s="250" t="n"/>
+      <c r="D1" s="250" t="n"/>
+      <c r="E1" s="250" t="n"/>
+      <c r="F1" s="250" t="n"/>
+      <c r="G1" s="250" t="n"/>
+      <c r="H1" s="250" t="n"/>
+      <c r="I1" s="250" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="236" t="inlineStr">
         <is>
@@ -18533,7 +18994,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
@@ -6475,7 +6475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="57" min="1" max="1"/>
@@ -6496,14 +6496,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
@@ -7049,14 +7041,6 @@
           <t>HIZLI BASLANGIC — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3"/>
@@ -7165,7 +7149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
@@ -7185,13 +7169,6 @@
           <t>NAKIT GIRISLERI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -8290,7 +8267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
@@ -8310,13 +8287,6 @@
           <t>NAKIT CIKISLARI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -9250,7 +9220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
@@ -9272,15 +9242,6 @@
           <t>HAFTALIK PLAN — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
-      <c r="J1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -10652,14 +10613,6 @@
           <t>MOTOR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="57">
       <c r="A2" s="108" t="inlineStr">
@@ -11247,8 +11200,8 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="cc3d"/>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:AN2"/>
     <mergeCell ref="A55:AN55"/>
-    <mergeCell ref="A2:AN2"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11263,7 +11216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="83" min="1" max="1"/>
@@ -11285,15 +11238,6 @@
           <t>KONTROLLER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
-      <c r="J1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -11500,7 +11444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="190.5" customWidth="1" style="83" min="1" max="1"/>
@@ -11521,14 +11465,6 @@
           <t>KARAR MOTORU — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -11612,7 +11548,7 @@
         </is>
       </c>
       <c r="B11" s="118">
-        <f>IF(B8="VERİ YOK","Önce giriş ve çıkış planlarını eksiksiz doldurun",IF(B6&gt;0,"Nakit akışı "&amp;B6&amp;". haftada tükeniyor: kritik ödemeleri erteleyin, tahsilatı hızlandırın, kısa vadeli kredi değerlendirin",IF(B7&gt;0,"Tampon eşiği aşılıyor: ertelenebilir giderleri listeleyin, tahsilat takvimini öne çekin","Plan sağlıklı: mevcut akış korunmalı")))</f>
+        <f>IF(B8="VERİ YOK","Önce giriş AND çıkış planlarını eksiksiz doldurun",IF(B6&gt;0,"Nakit akışı "&amp;B6&amp;". haftada tükeniyor: kritik ödemeleri erteleyin, tahsilatı hızlandırın, kısa vadeli kredi değerlendirin",IF(B7&gt;0,"Tampon eşiği aşılıyor: ertelenebilir giderleri listeleyin, tahsilat takvimini öne çekin","Plan sağlıklı: mevcut akış korunmalı")))</f>
         <v/>
       </c>
     </row>
@@ -11765,7 +11701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="159.5" customWidth="1" style="83" min="1" max="1"/>
@@ -11786,14 +11722,6 @@
           <t>SENARYO DUYARLILIK — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -12045,7 +11973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="98.5" customWidth="1" style="83" min="1" max="1"/>
@@ -12066,14 +11994,6 @@
           <t>RAPOR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -12264,7 +12184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
@@ -12395,7 +12315,7 @@
       <c r="I7" s="143" t="n"/>
       <c r="J7" s="143" t="n"/>
       <c r="K7" s="154">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="143" t="n"/>
@@ -12700,11 +12620,11 @@
         </is>
       </c>
       <c r="I19" s="243">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="244">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="168" t="inlineStr"/>
@@ -12850,7 +12770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="83" min="1" max="1"/>
@@ -12871,14 +12791,6 @@
           <t>ORNEK VERI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -13072,7 +12984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="96.5" customWidth="1" style="83" min="1" max="1"/>
@@ -13093,14 +13005,6 @@
           <t>TESTLER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -13261,7 +13165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.5" customWidth="1" style="83" min="1" max="1"/>
@@ -13282,14 +13186,6 @@
           <t>AKIS — OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="57">
@@ -13498,7 +13394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="83" min="1" max="1"/>
@@ -13519,14 +13415,6 @@
           <t>DEGISIKLIK KAYDI — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -13589,7 +13477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="83" min="1" max="1"/>
@@ -13610,14 +13498,6 @@
           <t>LISTELER — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -13809,14 +13689,6 @@
           <t>AYARLAR — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" s="57">
       <c r="A2" s="108" t="inlineStr">
@@ -14819,14 +14691,6 @@
           <t>KILAVUZ — 13 HAFTALIK NAKİT AKIŞI VE ÖDEME PLANLAMA SİSTEMİ</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
@@ -15104,7 +14968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
@@ -15568,7 +15432,7 @@
         </is>
       </c>
       <c r="E17" s="201">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -15591,7 +15455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
@@ -15758,7 +15622,7 @@
       <c r="C11" s="143" t="n"/>
       <c r="D11" s="143" t="n"/>
       <c r="E11" s="248">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="143" t="n"/>
@@ -15915,7 +15779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="57" min="1" max="1"/>
@@ -15936,14 +15800,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
@@ -16418,7 +16274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="57" min="1" max="1"/>
@@ -16439,14 +16295,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
@@ -17173,7 +17021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" style="57" min="1" max="1"/>
@@ -17194,14 +17042,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
@@ -17859,7 +17699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" style="57" min="1" max="1"/>
@@ -17880,14 +17720,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
@@ -18417,7 +18249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" style="57" min="1" max="1"/>
@@ -18438,14 +18270,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="250" t="n"/>
-      <c r="C1" s="250" t="n"/>
-      <c r="D1" s="250" t="n"/>
-      <c r="E1" s="250" t="n"/>
-      <c r="F1" s="250" t="n"/>
-      <c r="G1" s="250" t="n"/>
-      <c r="H1" s="250" t="n"/>
-      <c r="I1" s="250" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">

--- a/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
+++ b/EXCELARSIV_PRODUCTS/on-uc-haftalik-nakit-akisi-ve-odeme-planlama-sistemi/OnUcHaftalikNakitAkisiVeOdemePlanlamaSistemi.xlsx
@@ -120,7 +120,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="98">
+  <fonts count="134">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -727,8 +727,220 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -920,8 +1132,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="107">
     <border>
       <left/>
       <right/>
@@ -1283,6 +1519,737 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00065F46"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FCA5A5"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="0093C5FD"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -1294,7 +2261,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="400">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1966,6 +2933,269 @@
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="101" fillId="18" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="103" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="101" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="51" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="76" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="51" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="76" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="113" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="115" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="116" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="117" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="17" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="125" fillId="17" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="17" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="122" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="126" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="127" fillId="12" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="132" fillId="11" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="129" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="18" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="133" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="118" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="130" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="130" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="12" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="11" borderId="78" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="18" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6497,7 +7727,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="216" t="inlineStr">
         <is>
@@ -6762,7 +7991,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1" s="57">
       <c r="A26" s="219" t="inlineStr">
         <is>
@@ -6895,9 +8123,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="31.5" customHeight="1" s="57">
       <c r="A5" s="85" t="inlineStr">
         <is>
@@ -6912,8 +8137,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="87" t="inlineStr">
         <is>
@@ -6949,7 +8172,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="87" t="inlineStr">
         <is>
@@ -6964,7 +8186,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="87" t="inlineStr">
         <is>
@@ -6993,9 +8214,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="89" t="inlineStr">
         <is>
@@ -7042,9 +8260,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="19.5" customHeight="1" s="57">
       <c r="A5" s="90" t="inlineStr">
         <is>
@@ -7052,7 +8267,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="87" t="inlineStr">
         <is>
@@ -7098,9 +8312,6 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="57"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="87" t="inlineStr">
         <is>
@@ -7170,7 +8381,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -7178,7 +8388,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -8288,7 +9497,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -8296,7 +9504,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -9243,7 +10450,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -9256,7 +10462,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -10621,7 +11826,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="109" t="inlineStr">
         <is>
@@ -10860,8 +12064,6 @@
         <v/>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="110" t="inlineStr">
         <is>
@@ -10939,8 +12141,6 @@
         <v/>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" ht="15" customHeight="1" s="57">
       <c r="A37" s="109" t="inlineStr">
         <is>
@@ -11188,7 +12388,6 @@
         <v/>
       </c>
     </row>
-    <row r="54"/>
     <row r="55" ht="19.5" customHeight="1" s="57">
       <c r="A55" s="108" t="inlineStr">
         <is>
@@ -11239,7 +12438,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -11247,8 +12445,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="116" t="inlineStr">
         <is>
@@ -11381,10 +12577,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="36.75" customHeight="1" s="57">
       <c r="A22" s="103" t="inlineStr">
         <is>
@@ -11466,7 +12658,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -11474,7 +12665,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="119" t="inlineStr">
         <is>
@@ -11629,10 +12819,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23" ht="60.75" customHeight="1" s="57">
       <c r="A23" s="103" t="inlineStr">
         <is>
@@ -11723,7 +12909,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -11731,7 +12916,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="119" t="inlineStr">
         <is>
@@ -11817,7 +13001,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="125" t="inlineStr">
         <is>
@@ -11923,7 +13106,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="48.75" customHeight="1" s="57">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -11995,7 +13177,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -12036,7 +13217,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="125" t="inlineStr">
         <is>
@@ -12149,7 +13329,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21" ht="24.75" customHeight="1" s="57">
       <c r="A21" s="103" t="inlineStr">
         <is>
@@ -12187,578 +13366,623 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="57" min="1" max="1"/>
-    <col width="84.5" customWidth="1" style="57" min="2" max="2"/>
-    <col width="15" customWidth="1" style="57" min="3" max="3"/>
-    <col width="15.5" customWidth="1" style="57" min="4" max="4"/>
-    <col width="36.5" customWidth="1" style="57" min="5" max="5"/>
-    <col width="18" customWidth="1" style="57" min="6" max="6"/>
-    <col width="15.5" customWidth="1" style="57" min="7" max="7"/>
-    <col width="75.5" customWidth="1" style="57" min="8" max="8"/>
-    <col width="15" customWidth="1" style="57" min="9" max="9"/>
-    <col width="15.5" customWidth="1" style="57" min="10" max="10"/>
-    <col width="79.5" customWidth="1" style="57" min="11" max="11"/>
-    <col width="18" customWidth="1" style="57" min="12" max="12"/>
-    <col width="18" customWidth="1" style="57" min="13" max="13"/>
-    <col width="13" customWidth="1" style="57" min="14" max="14"/>
+    <col width="12" customWidth="1" style="57" min="1" max="1"/>
+    <col width="17" customWidth="1" style="57" min="2" max="2"/>
+    <col width="12" customWidth="1" style="57" min="3" max="3"/>
+    <col width="11" customWidth="1" style="57" min="4" max="4"/>
+    <col width="17" customWidth="1" style="57" min="5" max="5"/>
+    <col width="12" customWidth="1" style="57" min="6" max="6"/>
+    <col width="11" customWidth="1" style="57" min="7" max="7"/>
+    <col width="17" customWidth="1" style="57" min="8" max="8"/>
+    <col width="13" customWidth="1" style="57" min="9" max="9"/>
+    <col width="11" customWidth="1" style="57" min="10" max="10"/>
+    <col width="17" customWidth="1" style="57" min="11" max="11"/>
+    <col width="14" customWidth="1" style="57" min="12" max="12"/>
+    <col width="12" customWidth="1" style="57" min="13" max="13"/>
+    <col width="6" customWidth="1" style="57" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="57">
+      <c r="A1" s="269" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="138" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="57">
+      <c r="B2" s="270" t="inlineStr">
         <is>
           <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI</t>
         </is>
       </c>
-      <c r="L2" s="139" t="inlineStr">
+      <c r="L2" s="271" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="140" t="inlineStr">
+      <c r="M2" s="272" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="141" t="inlineStr">
-        <is>
-          <t>Hedef Kullanıcı: KOBİ sahipleri, finans yöneticileri, muhasebe sorumluları, mali müşavirler · 2026 Q3 Denetim Standardı</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="142" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="57">
+      <c r="B3" s="273" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1" s="57"/>
+    <row r="5" ht="20" customHeight="1" s="57">
+      <c r="B5" s="274" t="inlineStr">
         <is>
           <t>TOPLAM NAKİT HAVUZU</t>
         </is>
       </c>
-      <c r="C5" s="143" t="n"/>
-      <c r="D5" s="144" t="inlineStr">
+      <c r="C5" s="275" t="n"/>
+      <c r="D5" s="276" t="inlineStr">
         <is>
           <t>4 HESAP</t>
         </is>
       </c>
-      <c r="E5" s="145" t="inlineStr">
+      <c r="E5" s="277" t="inlineStr">
         <is>
           <t>BU AY ÖDENECEK ÇIKIŞ</t>
         </is>
       </c>
-      <c r="F5" s="143" t="n"/>
-      <c r="G5" s="146" t="inlineStr">
+      <c r="F5" s="275" t="n"/>
+      <c r="G5" s="278" t="inlineStr">
         <is>
           <t>VADE: 4 GÜN</t>
         </is>
       </c>
-      <c r="H5" s="142" t="inlineStr">
+      <c r="H5" s="279" t="inlineStr">
         <is>
           <t>NET SERBEST LİKİDİTE</t>
         </is>
       </c>
-      <c r="I5" s="143" t="n"/>
-      <c r="J5" s="147" t="inlineStr">
+      <c r="I5" s="275" t="n"/>
+      <c r="J5" s="280" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="148" t="inlineStr">
+      <c r="K5" s="281" t="inlineStr">
         <is>
           <t>DSCR / NAKİT DÖNGÜSÜ</t>
         </is>
       </c>
-      <c r="L5" s="143" t="n"/>
-      <c r="M5" s="144" t="inlineStr">
+      <c r="L5" s="275" t="n"/>
+      <c r="M5" s="282" t="inlineStr">
         <is>
           <t>EŞİK: 1.30x</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="149" t="n"/>
-      <c r="C6" s="143" t="n"/>
-      <c r="D6" s="143" t="n"/>
-      <c r="E6" s="150" t="n"/>
-      <c r="F6" s="143" t="n"/>
-      <c r="G6" s="143" t="n"/>
-      <c r="H6" s="149" t="n"/>
-      <c r="I6" s="143" t="n"/>
-      <c r="J6" s="143" t="n"/>
-      <c r="K6" s="151" t="n"/>
-      <c r="L6" s="143" t="n"/>
-      <c r="M6" s="143" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="239">
+    <row r="6" ht="6" customHeight="1" s="57">
+      <c r="B6" s="283" t="n"/>
+      <c r="C6" s="284" t="n"/>
+      <c r="D6" s="285" t="n"/>
+      <c r="E6" s="286" t="n"/>
+      <c r="F6" s="284" t="n"/>
+      <c r="G6" s="285" t="n"/>
+      <c r="H6" s="287" t="n"/>
+      <c r="I6" s="284" t="n"/>
+      <c r="J6" s="285" t="n"/>
+      <c r="K6" s="288" t="n"/>
+      <c r="L6" s="284" t="n"/>
+      <c r="M6" s="285" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="57">
+      <c r="B7" s="289">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="143" t="n"/>
-      <c r="D7" s="143" t="n"/>
-      <c r="E7" s="240">
+      <c r="C7" s="284" t="n"/>
+      <c r="D7" s="285" t="n"/>
+      <c r="E7" s="290">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="143" t="n"/>
-      <c r="G7" s="143" t="n"/>
-      <c r="H7" s="239">
+      <c r="F7" s="284" t="n"/>
+      <c r="G7" s="285" t="n"/>
+      <c r="H7" s="291">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="143" t="n"/>
-      <c r="J7" s="143" t="n"/>
-      <c r="K7" s="154">
+      <c r="I7" s="284" t="n"/>
+      <c r="J7" s="285" t="n"/>
+      <c r="K7" s="292">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="143" t="n"/>
-      <c r="M7" s="143" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="149" t="n"/>
-      <c r="C8" s="143" t="n"/>
-      <c r="D8" s="143" t="n"/>
-      <c r="E8" s="150" t="n"/>
-      <c r="F8" s="143" t="n"/>
-      <c r="G8" s="143" t="n"/>
-      <c r="H8" s="149" t="n"/>
-      <c r="I8" s="143" t="n"/>
-      <c r="J8" s="143" t="n"/>
-      <c r="K8" s="151" t="n"/>
-      <c r="L8" s="143" t="n"/>
-      <c r="M8" s="143" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="155" t="inlineStr">
+      <c r="L7" s="284" t="n"/>
+      <c r="M7" s="285" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1" s="57">
+      <c r="B8" s="283" t="n"/>
+      <c r="C8" s="284" t="n"/>
+      <c r="D8" s="285" t="n"/>
+      <c r="E8" s="286" t="n"/>
+      <c r="F8" s="284" t="n"/>
+      <c r="G8" s="285" t="n"/>
+      <c r="H8" s="287" t="n"/>
+      <c r="I8" s="284" t="n"/>
+      <c r="J8" s="285" t="n"/>
+      <c r="K8" s="288" t="n"/>
+      <c r="L8" s="284" t="n"/>
+      <c r="M8" s="285" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="57">
+      <c r="B9" s="293" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="143" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="156" t="inlineStr">
+      <c r="C9" s="294" t="n"/>
+      <c r="D9" s="295" t="n"/>
+      <c r="E9" s="296" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="143" t="n"/>
-      <c r="G9" s="143" t="n"/>
-      <c r="H9" s="155" t="inlineStr">
+      <c r="F9" s="294" t="n"/>
+      <c r="G9" s="295" t="n"/>
+      <c r="H9" s="297" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="143" t="n"/>
-      <c r="J9" s="143" t="n"/>
-      <c r="K9" s="157" t="inlineStr">
+      <c r="I9" s="294" t="n"/>
+      <c r="J9" s="295" t="n"/>
+      <c r="K9" s="298" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="143" t="n"/>
-      <c r="M9" s="143" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="81" t="inlineStr">
+      <c r="L9" s="294" t="n"/>
+      <c r="M9" s="295" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" s="57"/>
+    <row r="11" ht="24" customHeight="1" s="57">
+      <c r="B11" s="299" t="inlineStr">
         <is>
           <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="158" t="inlineStr">
+      <c r="F11" s="300" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="81" t="inlineStr">
+      <c r="H11" s="299" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="80" t="inlineStr">
+    <row r="12" ht="18" customHeight="1" s="57">
+      <c r="B12" s="141" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="80" t="inlineStr">
+      <c r="H12" s="141" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="159" t="inlineStr">
+    <row r="13" ht="8" customHeight="1" s="57"/>
+    <row r="14" ht="24" customHeight="1" s="57">
+      <c r="B14" s="301" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="159" t="inlineStr">
+      <c r="C14" s="301" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="159" t="inlineStr">
+      <c r="D14" s="301" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="159" t="inlineStr">
+      <c r="E14" s="301" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="160" t="inlineStr">
+      <c r="H14" s="302" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="160" t="inlineStr">
+      <c r="I14" s="303" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="160" t="inlineStr">
+      <c r="J14" s="303" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="160" t="inlineStr">
+      <c r="K14" s="303" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="160" t="inlineStr">
+      <c r="L14" s="303" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="80" t="inlineStr">
+      <c r="M14" s="303" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="57">
+      <c r="B15" s="304" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="80" t="n">
+      <c r="C15" s="304" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="80" t="n">
+      <c r="D15" s="304" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="80" t="n">
+      <c r="E15" s="304" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="161" t="inlineStr">
+      <c r="H15" s="305" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="241">
+      <c r="I15" s="306">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="242">
+      <c r="J15" s="307">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="163" t="inlineStr">
+      <c r="K15" s="308" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="147" t="inlineStr">
+      <c r="L15" s="309" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="80" t="inlineStr">
+      <c r="M15" s="310" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="57">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="80" t="n">
+      <c r="C16" s="311" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="80" t="n">
+      <c r="D16" s="311" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="80" t="n">
+      <c r="E16" s="311" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="161" t="inlineStr">
+      <c r="H16" s="312" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="241">
+      <c r="I16" s="313">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="242">
+      <c r="J16" s="314">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="163" t="inlineStr">
+      <c r="K16" s="315" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="144" t="inlineStr">
+      <c r="L16" s="316" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="80" t="inlineStr">
+      <c r="M16" s="317" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="57">
+      <c r="B17" s="304" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="80" t="n">
+      <c r="C17" s="304" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="80" t="n">
+      <c r="D17" s="304" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="80" t="n">
+      <c r="E17" s="304" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="161" t="inlineStr">
+      <c r="H17" s="305" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="241">
+      <c r="I17" s="306">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="242">
+      <c r="J17" s="307">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="163" t="inlineStr">
+      <c r="K17" s="308" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="164" t="inlineStr">
+      <c r="L17" s="318" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="80" t="inlineStr">
+      <c r="M17" s="310" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="57">
+      <c r="B18" s="311" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n">
+      <c r="C18" s="311" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="80" t="n">
+      <c r="D18" s="311" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="80" t="n">
+      <c r="E18" s="311" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="161" t="inlineStr">
+      <c r="H18" s="312" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="241">
+      <c r="I18" s="313">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="242">
+      <c r="J18" s="314">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="163" t="inlineStr">
+      <c r="K18" s="315" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="147" t="inlineStr">
+      <c r="L18" s="319" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="80" t="inlineStr">
+      <c r="M18" s="317" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1" s="57">
+      <c r="B19" s="304" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="80" t="n">
+      <c r="C19" s="304" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="80" t="n">
+      <c r="D19" s="304" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="80" t="n">
+      <c r="E19" s="304" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="165" t="inlineStr">
+      <c r="H19" s="320" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="243">
+      <c r="I19" s="321">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="244">
+      <c r="J19" s="322">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="168" t="inlineStr"/>
-      <c r="L19" s="169" t="inlineStr">
+      <c r="K19" s="323" t="inlineStr"/>
+      <c r="L19" s="324" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="M19" s="324" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="57">
+      <c r="B20" s="311" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
+      <c r="C20" s="311" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="80" t="n">
+      <c r="D20" s="311" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="80" t="n">
+      <c r="E20" s="311" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="170" t="inlineStr">
+    <row r="21" ht="14" customHeight="1" s="57"/>
+    <row r="22" ht="24" customHeight="1" s="57">
+      <c r="B22" s="325" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="170" t="inlineStr">
+      <c r="C22" s="275" t="n"/>
+      <c r="D22" s="275" t="n"/>
+      <c r="E22" s="326" t="n"/>
+      <c r="F22" s="325" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="171" t="inlineStr">
+      <c r="G22" s="275" t="n"/>
+      <c r="H22" s="275" t="n"/>
+      <c r="I22" s="326" t="n"/>
+      <c r="K22" s="327" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="172" t="n"/>
-      <c r="M22" s="172" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="65" t="inlineStr">
+      <c r="L22" s="328" t="n"/>
+      <c r="M22" s="329" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" s="57">
+      <c r="B23" s="330" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="80" t="inlineStr">
+      <c r="C23" s="284" t="n"/>
+      <c r="D23" s="284" t="n"/>
+      <c r="E23" s="285" t="n"/>
+      <c r="F23" s="331" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="173" t="inlineStr">
+      <c r="G23" s="284" t="n"/>
+      <c r="H23" s="284" t="n"/>
+      <c r="I23" s="332" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="174" t="inlineStr">
+      <c r="K23" s="333" t="inlineStr">
         <is>
           <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
         </is>
       </c>
-      <c r="L23" s="172" t="n"/>
-      <c r="M23" s="172" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="66" t="inlineStr">
+      <c r="L23" s="334" t="n"/>
+      <c r="M23" s="335" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" s="57">
+      <c r="B24" s="336" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="80" t="inlineStr">
+      <c r="C24" s="284" t="n"/>
+      <c r="D24" s="284" t="n"/>
+      <c r="E24" s="285" t="n"/>
+      <c r="F24" s="331" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="173" t="inlineStr">
+      <c r="G24" s="284" t="n"/>
+      <c r="H24" s="284" t="n"/>
+      <c r="I24" s="332" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="175" t="inlineStr">
-        <is>
-          <t>Atıl kalan nakit rezervinin değerlendirilmesiyle ek finansal getiri imkanı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="176" t="inlineStr">
+      <c r="K24" s="337" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+      <c r="M24" s="385" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" s="57">
+      <c r="B25" s="338" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="65" t="inlineStr">
+      <c r="C25" s="284" t="n"/>
+      <c r="D25" s="284" t="n"/>
+      <c r="E25" s="285" t="n"/>
+      <c r="F25" s="309" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="177" t="inlineStr">
+      <c r="G25" s="339" t="n"/>
+      <c r="H25" s="339" t="n"/>
+      <c r="I25" s="339" t="n"/>
+      <c r="K25" s="386" t="n"/>
+      <c r="M25" s="385" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" s="57">
+      <c r="B26" s="341" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="178" t="inlineStr">
+      <c r="C26" s="284" t="n"/>
+      <c r="D26" s="284" t="n"/>
+      <c r="E26" s="285" t="n"/>
+      <c r="F26" s="342" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
-      <c r="G26" s="251" t="n"/>
-      <c r="H26" s="251" t="n"/>
-      <c r="I26" s="252" t="n"/>
-      <c r="K26" s="179" t="inlineStr">
-        <is>
-          <t>FONLAMA SENARYOSUNU İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="F27" s="253" t="n"/>
-      <c r="G27" s="254" t="n"/>
-      <c r="H27" s="254" t="n"/>
-      <c r="I27" s="255" t="n"/>
+      <c r="G26" s="387" t="n"/>
+      <c r="H26" s="387" t="n"/>
+      <c r="I26" s="388" t="n"/>
+      <c r="K26" s="344" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+      <c r="L26" s="387" t="n"/>
+      <c r="M26" s="388" t="n"/>
+    </row>
+    <row r="27" ht="26" customHeight="1" s="57">
+      <c r="B27" s="345" t="n"/>
+      <c r="C27" s="294" t="n"/>
+      <c r="D27" s="294" t="n"/>
+      <c r="E27" s="295" t="n"/>
+      <c r="F27" s="389" t="n"/>
+      <c r="G27" s="390" t="n"/>
+      <c r="H27" s="390" t="n"/>
+      <c r="I27" s="391" t="n"/>
+      <c r="K27" s="389" t="n"/>
+      <c r="L27" s="390" t="n"/>
+      <c r="M27" s="391" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12792,7 +14016,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -12800,7 +14023,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -13006,7 +14228,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -13014,7 +14235,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -13137,9 +14357,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16" ht="24.75" customHeight="1" s="57">
       <c r="A16" s="103" t="inlineStr">
         <is>
@@ -13187,7 +14404,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="83" t="inlineStr">
         <is>
@@ -13365,7 +14581,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="83" t="inlineStr">
         <is>
@@ -13416,7 +14631,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -13424,7 +14638,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1" s="57">
       <c r="A5" s="94" t="inlineStr">
         <is>
@@ -13499,7 +14712,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -13507,7 +14719,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="106" t="inlineStr">
         <is>
@@ -13697,7 +14908,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="109" t="inlineStr">
         <is>
@@ -13805,7 +15015,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="109" t="inlineStr">
         <is>
@@ -14515,7 +15724,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="57">
       <c r="J34" s="83" t="inlineStr">
         <is>
@@ -14692,7 +15900,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1" s="57">
       <c r="A3" s="268" t="inlineStr">
         <is>
@@ -14700,7 +15907,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="125" t="inlineStr">
         <is>
@@ -14827,7 +16033,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="125" t="inlineStr">
         <is>
@@ -14863,7 +16068,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="125" t="inlineStr">
         <is>
@@ -14892,8 +16096,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36" ht="15" customHeight="1" s="57">
       <c r="A36" s="125" t="inlineStr">
         <is>
@@ -14990,7 +16192,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="180" t="inlineStr">
         <is>
@@ -15011,7 +16212,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="183" t="inlineStr">
         <is>
@@ -15424,7 +16624,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="200" t="inlineStr">
         <is>
@@ -15455,311 +16654,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="57" min="1" max="1"/>
+    <col width="12" customWidth="1" style="57" min="1" max="1"/>
     <col width="24" customWidth="1" style="57" min="2" max="2"/>
-    <col width="15" customWidth="1" style="57" min="3" max="3"/>
-    <col width="15" customWidth="1" style="57" min="4" max="4"/>
-    <col width="22" customWidth="1" style="57" min="5" max="5"/>
-    <col width="6" customWidth="1" style="57" min="6" max="6"/>
+    <col width="14" customWidth="1" style="57" min="3" max="3"/>
+    <col width="14" customWidth="1" style="57" min="4" max="4"/>
+    <col width="16" customWidth="1" style="57" min="5" max="5"/>
+    <col width="14" customWidth="1" style="57" min="6" max="6"/>
     <col width="6" customWidth="1" style="57" min="7" max="7"/>
     <col width="24" customWidth="1" style="57" min="8" max="8"/>
-    <col width="15" customWidth="1" style="57" min="9" max="9"/>
-    <col width="15" customWidth="1" style="57" min="10" max="10"/>
-    <col width="22" customWidth="1" style="57" min="11" max="11"/>
-    <col width="6" customWidth="1" style="57" min="12" max="12"/>
+    <col width="14" customWidth="1" style="57" min="9" max="9"/>
+    <col width="14" customWidth="1" style="57" min="10" max="10"/>
+    <col width="16" customWidth="1" style="57" min="11" max="11"/>
+    <col width="14" customWidth="1" style="57" min="12" max="12"/>
+    <col width="6" customWidth="1" style="57" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+    <row r="1" ht="24" customHeight="1" s="57">
+      <c r="A1" s="269" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1" s="57">
       <c r="B2" s="202" t="inlineStr">
         <is>
           <t>13 HAFTALIK NAKIT AKIŞI VE ÖDEME PLANLAMA SISTEMI — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="203" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="57">
+      <c r="B3" s="349" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · KOBİ sahipleri, finans yöneticileri, muhasebe sorumluları, mali müşavirler</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="204" t="inlineStr">
+    <row r="4" ht="20" customHeight="1" s="57">
+      <c r="B4" s="350" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="205" t="inlineStr">
+    <row r="5" ht="12" customHeight="1" s="57"/>
+    <row r="6" ht="26" customHeight="1" s="57">
+      <c r="B6" s="351" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="256" t="n"/>
-      <c r="D6" s="256" t="n"/>
-      <c r="E6" s="256" t="n"/>
-      <c r="F6" s="257" t="n"/>
-      <c r="H6" s="206" t="inlineStr">
+      <c r="C6" s="392" t="n"/>
+      <c r="D6" s="392" t="n"/>
+      <c r="E6" s="392" t="n"/>
+      <c r="F6" s="393" t="n"/>
+      <c r="H6" s="354" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="256" t="n"/>
-      <c r="J6" s="256" t="n"/>
-      <c r="K6" s="256" t="n"/>
-      <c r="L6" s="257" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="143" t="n"/>
-      <c r="C7" s="143" t="n"/>
-      <c r="D7" s="143" t="n"/>
-      <c r="E7" s="143" t="n"/>
-      <c r="F7" s="143" t="n"/>
-      <c r="H7" s="143" t="n"/>
-      <c r="I7" s="143" t="n"/>
-      <c r="J7" s="143" t="n"/>
-      <c r="K7" s="143" t="n"/>
-      <c r="L7" s="143" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="207" t="inlineStr">
+      <c r="I6" s="394" t="n"/>
+      <c r="J6" s="394" t="n"/>
+      <c r="K6" s="394" t="n"/>
+      <c r="L6" s="395" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" s="57">
+      <c r="B7" s="357" t="n"/>
+      <c r="C7" s="284" t="n"/>
+      <c r="D7" s="284" t="n"/>
+      <c r="E7" s="284" t="n"/>
+      <c r="F7" s="358" t="n"/>
+      <c r="H7" s="359" t="n"/>
+      <c r="I7" s="284" t="n"/>
+      <c r="J7" s="284" t="n"/>
+      <c r="K7" s="284" t="n"/>
+      <c r="L7" s="360" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="57">
+      <c r="B8" s="361" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="143" t="n"/>
-      <c r="D8" s="143" t="n"/>
-      <c r="E8" s="208" t="inlineStr">
+      <c r="C8" s="284" t="n"/>
+      <c r="D8" s="284" t="n"/>
+      <c r="E8" s="362" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="143" t="n"/>
-      <c r="H8" s="207" t="inlineStr">
+      <c r="F8" s="358" t="n"/>
+      <c r="H8" s="363" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="143" t="n"/>
-      <c r="J8" s="143" t="n"/>
-      <c r="K8" s="209" t="inlineStr">
+      <c r="I8" s="284" t="n"/>
+      <c r="J8" s="284" t="n"/>
+      <c r="K8" s="364" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="143" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="207" t="inlineStr">
+      <c r="L8" s="360" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" s="57">
+      <c r="B9" s="361" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="143" t="n"/>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="246">
+      <c r="C9" s="284" t="n"/>
+      <c r="D9" s="284" t="n"/>
+      <c r="E9" s="365">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="143" t="n"/>
-      <c r="H9" s="207" t="inlineStr">
+      <c r="F9" s="358" t="n"/>
+      <c r="H9" s="363" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="143" t="n"/>
-      <c r="J9" s="143" t="n"/>
-      <c r="K9" s="246">
+      <c r="I9" s="284" t="n"/>
+      <c r="J9" s="284" t="n"/>
+      <c r="K9" s="365">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="143" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="207" t="inlineStr">
+      <c r="L9" s="360" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="57">
+      <c r="B10" s="361" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="143" t="n"/>
-      <c r="D10" s="143" t="n"/>
-      <c r="E10" s="247">
+      <c r="C10" s="284" t="n"/>
+      <c r="D10" s="284" t="n"/>
+      <c r="E10" s="366">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="143" t="n"/>
-      <c r="H10" s="207" t="inlineStr">
+      <c r="F10" s="358" t="n"/>
+      <c r="H10" s="363" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="143" t="n"/>
-      <c r="J10" s="143" t="n"/>
-      <c r="K10" s="247">
+      <c r="I10" s="284" t="n"/>
+      <c r="J10" s="284" t="n"/>
+      <c r="K10" s="366">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="143" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="207" t="inlineStr">
+      <c r="L10" s="360" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="57">
+      <c r="B11" s="361" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="143" t="n"/>
-      <c r="D11" s="143" t="n"/>
-      <c r="E11" s="248">
+      <c r="C11" s="284" t="n"/>
+      <c r="D11" s="284" t="n"/>
+      <c r="E11" s="367">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="143" t="n"/>
-      <c r="H11" s="207" t="inlineStr">
+      <c r="F11" s="358" t="n"/>
+      <c r="H11" s="363" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="143" t="n"/>
-      <c r="J11" s="143" t="n"/>
-      <c r="K11" s="211" t="inlineStr">
+      <c r="I11" s="284" t="n"/>
+      <c r="J11" s="284" t="n"/>
+      <c r="K11" s="368" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="143" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="143" t="n"/>
-      <c r="C12" s="143" t="n"/>
-      <c r="D12" s="143" t="n"/>
-      <c r="E12" s="143" t="n"/>
-      <c r="F12" s="143" t="n"/>
-      <c r="H12" s="143" t="n"/>
-      <c r="I12" s="143" t="n"/>
-      <c r="J12" s="143" t="n"/>
-      <c r="K12" s="143" t="n"/>
-      <c r="L12" s="143" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="143" t="n"/>
-      <c r="C13" s="143" t="n"/>
-      <c r="D13" s="143" t="n"/>
-      <c r="E13" s="143" t="n"/>
-      <c r="F13" s="143" t="n"/>
-      <c r="H13" s="143" t="n"/>
-      <c r="I13" s="143" t="n"/>
-      <c r="J13" s="143" t="n"/>
-      <c r="K13" s="143" t="n"/>
-      <c r="L13" s="143" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="212" t="inlineStr">
+      <c r="L11" s="360" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="57">
+      <c r="B12" s="357" t="n"/>
+      <c r="C12" s="284" t="n"/>
+      <c r="D12" s="284" t="n"/>
+      <c r="E12" s="284" t="n"/>
+      <c r="F12" s="358" t="n"/>
+      <c r="H12" s="359" t="n"/>
+      <c r="I12" s="284" t="n"/>
+      <c r="J12" s="284" t="n"/>
+      <c r="K12" s="284" t="n"/>
+      <c r="L12" s="360" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="57">
+      <c r="B13" s="357" t="n"/>
+      <c r="C13" s="284" t="n"/>
+      <c r="D13" s="284" t="n"/>
+      <c r="E13" s="284" t="n"/>
+      <c r="F13" s="358" t="n"/>
+      <c r="H13" s="359" t="n"/>
+      <c r="I13" s="284" t="n"/>
+      <c r="J13" s="284" t="n"/>
+      <c r="K13" s="284" t="n"/>
+      <c r="L13" s="360" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="57">
+      <c r="B14" s="369" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="258" t="n"/>
-      <c r="D14" s="258" t="n"/>
-      <c r="E14" s="258" t="n"/>
-      <c r="F14" s="259" t="n"/>
-      <c r="H14" s="213" t="inlineStr">
+      <c r="C14" s="396" t="n"/>
+      <c r="D14" s="396" t="n"/>
+      <c r="E14" s="396" t="n"/>
+      <c r="F14" s="397" t="n"/>
+      <c r="H14" s="372" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="260" t="n"/>
-      <c r="J14" s="260" t="n"/>
-      <c r="K14" s="260" t="n"/>
-      <c r="L14" s="261" t="n"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="262" t="n"/>
-      <c r="C15" s="263" t="n"/>
-      <c r="D15" s="263" t="n"/>
-      <c r="E15" s="263" t="n"/>
-      <c r="F15" s="264" t="n"/>
-      <c r="H15" s="265" t="n"/>
-      <c r="I15" s="266" t="n"/>
-      <c r="J15" s="266" t="n"/>
-      <c r="K15" s="266" t="n"/>
-      <c r="L15" s="267" t="n"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="68" t="inlineStr">
+      <c r="I14" s="398" t="n"/>
+      <c r="J14" s="398" t="n"/>
+      <c r="K14" s="398" t="n"/>
+      <c r="L14" s="399" t="n"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" s="57">
+      <c r="B15" s="379" t="n"/>
+      <c r="C15" s="380" t="n"/>
+      <c r="D15" s="380" t="n"/>
+      <c r="E15" s="380" t="n"/>
+      <c r="F15" s="381" t="n"/>
+      <c r="H15" s="382" t="n"/>
+      <c r="I15" s="383" t="n"/>
+      <c r="J15" s="383" t="n"/>
+      <c r="K15" s="383" t="n"/>
+      <c r="L15" s="384" t="n"/>
+    </row>
+    <row r="16" ht="10" customHeight="1" s="57"/>
+    <row r="17" ht="26" customHeight="1" s="57">
+      <c r="B17" s="375" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="170" t="inlineStr">
+      <c r="C17" s="275" t="n"/>
+      <c r="D17" s="275" t="n"/>
+      <c r="E17" s="275" t="n"/>
+      <c r="F17" s="275" t="n"/>
+      <c r="G17" s="275" t="n"/>
+      <c r="H17" s="275" t="n"/>
+      <c r="I17" s="275" t="n"/>
+      <c r="J17" s="275" t="n"/>
+      <c r="K17" s="275" t="n"/>
+      <c r="L17" s="326" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="57">
+      <c r="B18" s="376" t="n"/>
+      <c r="C18" s="284" t="n"/>
+      <c r="D18" s="284" t="n"/>
+      <c r="E18" s="284" t="n"/>
+      <c r="F18" s="284" t="n"/>
+      <c r="G18" s="284" t="n"/>
+      <c r="H18" s="284" t="n"/>
+      <c r="I18" s="284" t="n"/>
+      <c r="J18" s="284" t="n"/>
+      <c r="K18" s="284" t="n"/>
+      <c r="L18" s="285" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="57">
+      <c r="B19" s="377" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="214" t="inlineStr">
+      <c r="C19" s="284" t="n"/>
+      <c r="D19" s="284" t="n"/>
+      <c r="E19" s="284" t="n"/>
+      <c r="F19" s="284" t="n"/>
+      <c r="G19" s="284" t="n"/>
+      <c r="H19" s="284" t="n"/>
+      <c r="I19" s="284" t="n"/>
+      <c r="J19" s="284" t="n"/>
+      <c r="K19" s="284" t="n"/>
+      <c r="L19" s="285" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="57">
+      <c r="B20" s="378" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="170" t="inlineStr">
+      <c r="C20" s="284" t="n"/>
+      <c r="D20" s="284" t="n"/>
+      <c r="E20" s="284" t="n"/>
+      <c r="F20" s="284" t="n"/>
+      <c r="G20" s="284" t="n"/>
+      <c r="H20" s="284" t="n"/>
+      <c r="I20" s="284" t="n"/>
+      <c r="J20" s="284" t="n"/>
+      <c r="K20" s="284" t="n"/>
+      <c r="L20" s="285" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="57">
+      <c r="B21" s="377" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="214" t="inlineStr">
+      <c r="C21" s="284" t="n"/>
+      <c r="D21" s="284" t="n"/>
+      <c r="E21" s="284" t="n"/>
+      <c r="F21" s="284" t="n"/>
+      <c r="G21" s="284" t="n"/>
+      <c r="H21" s="284" t="n"/>
+      <c r="I21" s="284" t="n"/>
+      <c r="J21" s="284" t="n"/>
+      <c r="K21" s="284" t="n"/>
+      <c r="L21" s="285" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="57">
+      <c r="B22" s="378" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="170" t="inlineStr">
+      <c r="C22" s="284" t="n"/>
+      <c r="D22" s="284" t="n"/>
+      <c r="E22" s="284" t="n"/>
+      <c r="F22" s="284" t="n"/>
+      <c r="G22" s="284" t="n"/>
+      <c r="H22" s="284" t="n"/>
+      <c r="I22" s="284" t="n"/>
+      <c r="J22" s="284" t="n"/>
+      <c r="K22" s="284" t="n"/>
+      <c r="L22" s="285" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="57">
+      <c r="B23" s="377" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="214" t="inlineStr">
+      <c r="C23" s="284" t="n"/>
+      <c r="D23" s="284" t="n"/>
+      <c r="E23" s="284" t="n"/>
+      <c r="F23" s="284" t="n"/>
+      <c r="G23" s="284" t="n"/>
+      <c r="H23" s="284" t="n"/>
+      <c r="I23" s="284" t="n"/>
+      <c r="J23" s="284" t="n"/>
+      <c r="K23" s="284" t="n"/>
+      <c r="L23" s="285" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" s="57">
+      <c r="B24" s="378" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="170" t="inlineStr">
+      <c r="C24" s="284" t="n"/>
+      <c r="D24" s="284" t="n"/>
+      <c r="E24" s="284" t="n"/>
+      <c r="F24" s="284" t="n"/>
+      <c r="G24" s="284" t="n"/>
+      <c r="H24" s="284" t="n"/>
+      <c r="I24" s="284" t="n"/>
+      <c r="J24" s="284" t="n"/>
+      <c r="K24" s="284" t="n"/>
+      <c r="L24" s="285" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" s="57">
+      <c r="B25" s="377" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="214" t="inlineStr">
+      <c r="C25" s="284" t="n"/>
+      <c r="D25" s="284" t="n"/>
+      <c r="E25" s="284" t="n"/>
+      <c r="F25" s="284" t="n"/>
+      <c r="G25" s="284" t="n"/>
+      <c r="H25" s="284" t="n"/>
+      <c r="I25" s="284" t="n"/>
+      <c r="J25" s="284" t="n"/>
+      <c r="K25" s="284" t="n"/>
+      <c r="L25" s="285" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" s="57">
+      <c r="B26" s="378" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="284" t="n"/>
+      <c r="D26" s="284" t="n"/>
+      <c r="E26" s="284" t="n"/>
+      <c r="F26" s="284" t="n"/>
+      <c r="G26" s="284" t="n"/>
+      <c r="H26" s="284" t="n"/>
+      <c r="I26" s="284" t="n"/>
+      <c r="J26" s="284" t="n"/>
+      <c r="K26" s="284" t="n"/>
+      <c r="L26" s="285" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="57">
+      <c r="B27" s="345" t="n"/>
+      <c r="C27" s="294" t="n"/>
+      <c r="D27" s="294" t="n"/>
+      <c r="E27" s="294" t="n"/>
+      <c r="F27" s="294" t="n"/>
+      <c r="G27" s="294" t="n"/>
+      <c r="H27" s="294" t="n"/>
+      <c r="I27" s="294" t="n"/>
+      <c r="J27" s="294" t="n"/>
+      <c r="K27" s="294" t="n"/>
+      <c r="L27" s="295" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -15801,7 +17116,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="221" t="inlineStr">
         <is>
@@ -16296,7 +17610,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="224" t="inlineStr">
         <is>
@@ -17043,7 +18356,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="229" t="inlineStr">
         <is>
@@ -17721,7 +19033,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="233" t="inlineStr">
         <is>
@@ -18271,7 +19582,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1" s="57">
       <c r="A3" s="236" t="inlineStr">
         <is>
